--- a/data/history_agent/source2_knowledge_base.xlsx
+++ b/data/history_agent/source2_knowledge_base.xlsx
@@ -1943,7 +1943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E200"/>
+  <dimension ref="A1:F303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1951,6 +1951,7 @@
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="85" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1979,6 +1980,11 @@
           <t>source_url</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>source_url_encoded</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2006,6 +2012,11 @@
           <t>https://he.wikipedia.org/wiki/לאומיות</t>
         </is>
       </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9C%D7%90%D7%95%D7%9E%D7%99%D7%95%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2033,6 +2044,11 @@
           <t>https://he.wikipedia.org/wiki/לאומיות</t>
         </is>
       </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9C%D7%90%D7%95%D7%9E%D7%99%D7%95%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2060,6 +2076,11 @@
           <t>https://he.wikipedia.org/wiki/מדינת_לאום</t>
         </is>
       </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%93%D7%99%D7%A0%D7%AA_%D7%9C%D7%90%D7%95%D7%9D</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2087,6 +2108,11 @@
           <t>https://he.wikipedia.org/wiki/לאומיות</t>
         </is>
       </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9C%D7%90%D7%95%D7%9E%D7%99%D7%95%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2114,6 +2140,11 @@
           <t>https://campus.ort.org.il/mod/book/view.php?id=8124</t>
         </is>
       </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8124</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2141,6 +2172,11 @@
           <t>https://he.wikipedia.org/wiki/רומנטיקה</t>
         </is>
       </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A8%D7%95%D7%9E%D7%A0%D7%98%D7%99%D7%A7%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2168,6 +2204,11 @@
           <t>https://he.wikipedia.org/wiki/לאומיות</t>
         </is>
       </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9C%D7%90%D7%95%D7%9E%D7%99%D7%95%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2195,6 +2236,11 @@
           <t>https://he.wikipedia.org/wiki/אביב_העמים</t>
         </is>
       </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%91%D7%99%D7%91_%D7%94%D7%A2%D7%9E%D7%99%D7%9D</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2222,6 +2268,11 @@
           <t>https://campus.ort.org.il/mod/book/view.php?id=8124</t>
         </is>
       </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8124</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2249,6 +2300,11 @@
           <t>https://he.wikipedia.org/wiki/בנימין_זאב_הרצל</t>
         </is>
       </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%91%D7%A0%D7%99%D7%9E%D7%99%D7%9F_%D7%96%D7%90%D7%91_%D7%94%D7%A8%D7%A6%D7%9C</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2276,6 +2332,11 @@
           <t>https://he.wikipedia.org/wiki/מדינת_היהודים</t>
         </is>
       </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%93%D7%99%D7%A0%D7%AA_%D7%94%D7%99%D7%94%D7%95%D7%93%D7%99%D7%9D</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2303,6 +2364,11 @@
           <t>https://he.wikipedia.org/wiki/הקונגרס_הציוני_העולמי_הראשון</t>
         </is>
       </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A7%D7%95%D7%A0%D7%92%D7%A8%D7%A1_%D7%94%D7%A6%D7%99%D7%95%D7%A0%D7%99_%D7%94%D7%A2%D7%95%D7%9C%D7%9E%D7%99_%D7%94%D7%A8%D7%90%D7%A9%D7%95%D7%9F</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2330,6 +2396,11 @@
           <t>https://he.wikipedia.org/wiki/ההסתדרות_הציונית</t>
         </is>
       </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%94%D7%A1%D7%AA%D7%93%D7%A8%D7%95%D7%AA_%D7%94%D7%A6%D7%99%D7%95%D7%A0%D7%99%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2357,6 +2428,11 @@
           <t>https://he.wikipedia.org/wiki/בנימין_זאב_הרצל</t>
         </is>
       </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%91%D7%A0%D7%99%D7%9E%D7%99%D7%9F_%D7%96%D7%90%D7%91_%D7%94%D7%A8%D7%A6%D7%9C</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2384,6 +2460,11 @@
           <t>https://he.wikipedia.org/wiki/תוכנית_אוגנדה</t>
         </is>
       </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%AA%D7%95%D7%9B%D7%A0%D7%99%D7%AA_%D7%90%D7%95%D7%92%D7%A0%D7%93%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2411,6 +2492,11 @@
           <t>https://campus.ort.org.il/mod/book/view.php?id=8170</t>
         </is>
       </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8170</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2438,6 +2524,11 @@
           <t>https://campus.ort.org.il/mod/book/view.php?id=8170</t>
         </is>
       </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8170</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2465,6 +2556,11 @@
           <t>https://he.wikipedia.org/wiki/השומר</t>
         </is>
       </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A9%D7%95%D7%9E%D7%A8</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2492,6 +2588,11 @@
           <t>https://campus.ort.org.il/mod/book/view.php?id=8170</t>
         </is>
       </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8170</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2519,6 +2620,11 @@
           <t>https://he.wikipedia.org/wiki/אליעזר_בן_יהודה</t>
         </is>
       </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%9C%D7%99%D7%A2%D7%96%D7%A8_%D7%91%D7%9F_%D7%99%D7%94%D7%95%D7%93%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2546,6 +2652,11 @@
           <t>https://campus.ort.org.il/mod/book/view.php?id=8173&amp;chapterid=759</t>
         </is>
       </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8173&amp;chapterid=759</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2573,6 +2684,11 @@
           <t>https://campus.ort.org.il/mod/book/view.php?id=8173&amp;chapterid=759</t>
         </is>
       </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8173&amp;chapterid=759</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2600,6 +2716,11 @@
           <t>https://campus.ort.org.il/mod/book/view.php?id=8173&amp;chapterid=759</t>
         </is>
       </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8173&amp;chapterid=759</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2627,6 +2748,11 @@
           <t>https://campus.ort.org.il/mod/book/view.php?id=8173&amp;chapterid=759</t>
         </is>
       </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8173&amp;chapterid=759</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2654,6 +2780,11 @@
           <t>https://campus.ort.org.il/mod/book/view.php?id=8173&amp;chapterid=759</t>
         </is>
       </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8173&amp;chapterid=759</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2681,6 +2812,11 @@
           <t>https://campus.ort.org.il/mod/book/view.php?id=8173&amp;chapterid=759</t>
         </is>
       </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8173&amp;chapterid=759</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2708,6 +2844,11 @@
           <t>https://www.yadvashem.org/he/education/lomdim-labagrut/nazi-ideology/nazi-ideology-1.html</t>
         </is>
       </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yadvashem.org/he/education/lomdim-labagrut/nazi-ideology/nazi-ideology-1.html</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2735,6 +2876,11 @@
           <t>https://campus.ort.org.il/mod/book/view.php?id=8124</t>
         </is>
       </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8124</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2762,6 +2908,11 @@
           <t>https://www.yadvashem.org/he/education/lomdim-labagrut/nazi-ideology/nazi-ideology-1.html</t>
         </is>
       </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yadvashem.org/he/education/lomdim-labagrut/nazi-ideology/nazi-ideology-1.html</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2789,6 +2940,11 @@
           <t>https://campus.ort.org.il/mod/book/view.php?id=8124</t>
         </is>
       </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8124</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2816,6 +2972,11 @@
           <t>https://www.yadvashem.org/he/education/lomdim-labagrut/nazi-ideology/nazi-ideology-1.html</t>
         </is>
       </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yadvashem.org/he/education/lomdim-labagrut/nazi-ideology/nazi-ideology-1.html</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2843,6 +3004,11 @@
           <t>https://he.wikipedia.org/wiki/תעמולה_נאצית</t>
         </is>
       </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%AA%D7%A2%D7%9E%D7%95%D7%9C%D7%94_%D7%A0%D7%90%D7%A6%D7%99%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2870,6 +3036,11 @@
           <t>https://he.wikipedia.org/wiki/גרמניה_הנאצית</t>
         </is>
       </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%92%D7%A8%D7%9E%D7%A0%D7%99%D7%94_%D7%94%D7%A0%D7%90%D7%A6%D7%99%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2897,6 +3068,11 @@
           <t>https://he.wikipedia.org/wiki/גרמניה_הנאצית</t>
         </is>
       </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%92%D7%A8%D7%9E%D7%A0%D7%99%D7%94_%D7%94%D7%A0%D7%90%D7%A6%D7%99%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2924,6 +3100,11 @@
           <t>https://he.wikipedia.org/wiki/חוקי_נירנברג</t>
         </is>
       </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%97%D7%95%D7%A7%D7%99_%D7%A0%D7%99%D7%A8%D7%A0%D7%91%D7%A8%D7%92</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2951,6 +3132,11 @@
           <t>https://he.wikipedia.org/wiki/אריזציה</t>
         </is>
       </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%A8%D7%99%D7%96%D7%A6%D7%99%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2978,6 +3164,11 @@
           <t>https://he.wikipedia.org/wiki/ליל_הבדולח</t>
         </is>
       </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9C%D7%99%D7%9C_%D7%94%D7%91%D7%93%D7%95%D7%9C%D7%97</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3005,6 +3196,11 @@
           <t>https://www.yadvashem.org/he/education/lomdim-labagrut/beginning-of-the-persecution/world-war-two-3.html</t>
         </is>
       </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yadvashem.org/he/education/lomdim-labagrut/beginning-of-the-persecution/world-war-two-3.html</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3032,6 +3228,11 @@
           <t>https://www.yadvashem.org/he/education/lomdim-labagrut/beginning-of-the-persecution/world-war-two-3.html</t>
         </is>
       </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yadvashem.org/he/education/lomdim-labagrut/beginning-of-the-persecution/world-war-two-3.html</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3059,6 +3260,11 @@
           <t>https://he.wikipedia.org/wiki/יודנראט</t>
         </is>
       </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%99%D7%95%D7%93%D7%A0%D7%A8%D7%90%D7%98</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3086,6 +3292,11 @@
           <t>https://www.yadvashem.org/he/education/lomdim-labagrut/beginning-of-the-persecution/world-war-two-3.html</t>
         </is>
       </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yadvashem.org/he/education/lomdim-labagrut/beginning-of-the-persecution/world-war-two-3.html</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3113,6 +3324,11 @@
           <t>https://www.yadvashem.org/he/education/lomdim-labagrut/beginning-of-the-persecution/world-war-two-3.html</t>
         </is>
       </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yadvashem.org/he/education/lomdim-labagrut/beginning-of-the-persecution/world-war-two-3.html</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3140,6 +3356,11 @@
           <t>https://www.yadvashem.org/he/education/educational-materials/learning-environment/warsaw-ghetto-interactive.html</t>
         </is>
       </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yadvashem.org/he/education/educational-materials/learning-environment/warsaw-ghetto-interactive.html</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3167,6 +3388,11 @@
           <t>https://www.yadvashem.org/he/education/educational-materials/learning-environment/warsaw-ghetto-interactive.html</t>
         </is>
       </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yadvashem.org/he/education/educational-materials/learning-environment/warsaw-ghetto-interactive.html</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3194,6 +3420,11 @@
           <t>https://www.yadvashem.org/he/education/lomdim-labagrut/murder-final-solution/final-solution-3.html</t>
         </is>
       </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yadvashem.org/he/education/lomdim-labagrut/murder-final-solution/final-solution-3.html</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3221,6 +3452,11 @@
           <t>https://he.wikipedia.org/wiki/המרד_הגדול</t>
         </is>
       </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A8%D7%93_%D7%94%D7%92%D7%93%D7%95%D7%9C</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3248,6 +3484,11 @@
           <t>https://he.wikipedia.org/wiki/המרד_הגדול</t>
         </is>
       </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A8%D7%93_%D7%94%D7%92%D7%93%D7%95%D7%9C</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3275,6 +3516,11 @@
           <t>https://he.wikipedia.org/wiki/המרד_הגדול</t>
         </is>
       </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A8%D7%93_%D7%94%D7%92%D7%93%D7%95%D7%9C</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3302,6 +3548,11 @@
           <t>https://he.wikipedia.org/wiki/המרד_הגדול</t>
         </is>
       </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A8%D7%93_%D7%94%D7%92%D7%93%D7%95%D7%9C</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3329,6 +3580,11 @@
           <t>https://he.wikipedia.org/wiki/רבן_יוחנן_בן_זכאי</t>
         </is>
       </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A8%D7%91%D7%9F_%D7%99%D7%95%D7%97%D7%A0%D7%9F_%D7%91%D7%9F_%D7%96%D7%9B%D7%90%D7%99</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3356,6 +3612,11 @@
           <t>https://he.wikipedia.org/wiki/יבנה</t>
         </is>
       </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%99%D7%91%D7%A0%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3383,6 +3644,11 @@
           <t>https://he.wikipedia.org/wiki/רבן_יוחנן_בן_זכאי</t>
         </is>
       </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A8%D7%91%D7%9F_%D7%99%D7%95%D7%97%D7%A0%D7%9F_%D7%91%D7%9F_%D7%96%D7%9B%D7%90%D7%99</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3410,6 +3676,11 @@
           <t>https://he.wikipedia.org/wiki/רבן_יוחנן_בן_זכאי</t>
         </is>
       </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A8%D7%91%D7%9F_%D7%99%D7%95%D7%97%D7%A0%D7%9F_%D7%91%D7%9F_%D7%96%D7%9B%D7%90%D7%99</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3437,6 +3708,11 @@
           <t>https://he.wikipedia.org/wiki/בגדאד</t>
         </is>
       </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%91%D7%92%D7%93%D7%90%D7%93</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3464,6 +3740,11 @@
           <t>https://he.wikipedia.org/wiki/בגדאד</t>
         </is>
       </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%91%D7%92%D7%93%D7%90%D7%93</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3491,6 +3772,11 @@
           <t>https://he.wikipedia.org/wiki/בית_החוכמה</t>
         </is>
       </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%91%D7%99%D7%AA_%D7%94%D7%97%D7%95%D7%9B%D7%9E%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3518,6 +3804,11 @@
           <t>https://he.wikipedia.org/wiki/בית_החוכמה</t>
         </is>
       </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%91%D7%99%D7%AA_%D7%94%D7%97%D7%95%D7%9B%D7%9E%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3545,6 +3836,11 @@
           <t>https://he.wikipedia.org/wiki/ד'ימי</t>
         </is>
       </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%93%27%D7%99%D7%9E%D7%99</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3572,6 +3868,11 @@
           <t>https://he.wikipedia.org/wiki/תנאי_עומר</t>
         </is>
       </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%AA%D7%A0%D7%90%D7%99_%D7%A2%D7%95%D7%9E%D7%A8</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3599,6 +3900,11 @@
           <t>https://he.wikipedia.org/wiki/ד'ימי</t>
         </is>
       </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%93%27%D7%99%D7%9E%D7%99</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3626,6 +3932,11 @@
           <t>https://he.wikipedia.org/wiki/פראג</t>
         </is>
       </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A4%D7%A8%D7%90%D7%92</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3653,6 +3964,11 @@
           <t>https://he.wikipedia.org/wiki/פראג</t>
         </is>
       </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A4%D7%A8%D7%90%D7%92</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3680,6 +3996,11 @@
           <t>https://he.wikipedia.org/wiki/אנטישמיות</t>
         </is>
       </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%A0%D7%98%D7%99%D7%A9%D7%9E%D7%99%D7%95%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3707,6 +4028,11 @@
           <t>https://he.wikipedia.org/wiki/פראג</t>
         </is>
       </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A4%D7%A8%D7%90%D7%92</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3734,6 +4060,11 @@
           <t>https://he.wikipedia.org/wiki/רבנו_גרשום</t>
         </is>
       </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A8%D7%91%D7%A0%D7%95_%D7%92%D7%A8%D7%A9%D7%95%D7%9D</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3761,6 +4092,11 @@
           <t>https://he.wikipedia.org/wiki/המנדט_הבריטי</t>
         </is>
       </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A0%D7%93%D7%98_%D7%94%D7%91%D7%A8%D7%99%D7%98%D7%99</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3788,6 +4124,11 @@
           <t>https://he.wikipedia.org/wiki/הספר_הלבן_(1939)</t>
         </is>
       </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A1%D7%A4%D7%A8_%D7%94%D7%9C%D7%91%D7%9F_%281939%29</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3815,6 +4156,11 @@
           <t>https://he.wikipedia.org/wiki/תנועת_המרי_העברי</t>
         </is>
       </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%AA%D7%A0%D7%95%D7%A2%D7%AA_%D7%94%D7%9E%D7%A8%D7%99_%D7%94%D7%A2%D7%91%D7%A8%D7%99</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3842,6 +4188,11 @@
           <t>https://he.wikipedia.org/wiki/תוכנית_החלוקה</t>
         </is>
       </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%AA%D7%95%D7%9B%D7%A0%D7%99%D7%AA_%D7%94%D7%97%D7%9C%D7%95%D7%A7%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3869,6 +4220,11 @@
           <t>https://he.wikipedia.org/wiki/מלחמת_העצמאות</t>
         </is>
       </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%9C%D7%97%D7%9E%D7%AA_%D7%94%D7%A2%D7%A6%D7%9E%D7%90%D7%95%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3896,6 +4252,11 @@
           <t>https://he.wikipedia.org/wiki/הכרזת_העצמאות</t>
         </is>
       </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9B%D7%A8%D7%96%D7%AA_%D7%94%D7%A2%D7%A6%D7%9E%D7%90%D7%95%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3923,6 +4284,11 @@
           <t>https://he.wikipedia.org/wiki/העלייה_ההמונית</t>
         </is>
       </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A2%D7%9C%D7%99%D7%99%D7%94_%D7%94%D7%94%D7%9E%D7%95%D7%A0%D7%99%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3950,6 +4316,11 @@
           <t>https://he.wikipedia.org/wiki/מדינת_ישראל</t>
         </is>
       </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%93%D7%99%D7%A0%D7%AA_%D7%99%D7%A9%D7%A8%D7%90%D7%9C</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3977,6 +4348,11 @@
           <t>https://he.wikipedia.org/wiki/עידן_הנאורות</t>
         </is>
       </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A2%D7%99%D7%93%D7%9F_%D7%94%D7%A0%D7%90%D7%95%D7%A8%D7%95%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4004,6 +4380,11 @@
           <t>https://he.wikipedia.org/wiki/המהפכה_הצרפתית</t>
         </is>
       </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%94%D7%A4%D7%9B%D7%94_%D7%94%D7%A6%D7%A8%D7%A4%D7%AA%D7%99%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4031,6 +4412,11 @@
           <t>https://he.wikipedia.org/wiki/נפוליאון_בונפרטה</t>
         </is>
       </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A0%D7%A4%D7%95%D7%9C%D7%99%D7%90%D7%95%D7%9F_%D7%91%D7%95%D7%A0%D7%A4%D7%A8%D7%98%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4058,6 +4444,11 @@
           <t>https://he.wikipedia.org/wiki/התנועה_הרומנטית</t>
         </is>
       </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%AA%D7%A0%D7%95%D7%A2%D7%94_%D7%94%D7%A8%D7%95%D7%9E%D7%A0%D7%98%D7%99%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4085,6 +4476,11 @@
           <t>https://he.wikipedia.org/wiki/המהפכה_התעשייתית</t>
         </is>
       </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%94%D7%A4%D7%9B%D7%94_%D7%94%D7%AA%D7%A2%D7%A9%D7%99%D7%99%D7%AA%D7%99%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4112,6 +4508,11 @@
           <t>https://he.wikipedia.org/wiki/ליברליזם</t>
         </is>
       </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9C%D7%99%D7%91%D7%A8%D7%9C%D7%99%D7%96%D7%9D</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4139,6 +4540,11 @@
           <t>https://he.wikipedia.org/wiki/מדינת_לאום</t>
         </is>
       </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%93%D7%99%D7%A0%D7%AA_%D7%9C%D7%90%D7%95%D7%9D</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4166,6 +4572,11 @@
           <t>https://he.wikipedia.org/wiki/אביב_העמים</t>
         </is>
       </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%91%D7%99%D7%91_%D7%94%D7%A2%D7%9E%D7%99%D7%9D</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -4193,6 +4604,11 @@
           <t>https://he.wikipedia.org/wiki/אביב_העמים</t>
         </is>
       </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%91%D7%99%D7%91_%D7%94%D7%A2%D7%9E%D7%99%D7%9D</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -4220,6 +4636,11 @@
           <t>https://he.wikipedia.org/wiki/איחוד_איטליה</t>
         </is>
       </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%99%D7%97%D7%95%D7%93_%D7%90%D7%99%D7%98%D7%9C%D7%99%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -4247,6 +4668,11 @@
           <t>https://he.wikipedia.org/wiki/איחוד_איטליה</t>
         </is>
       </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%99%D7%97%D7%95%D7%93_%D7%90%D7%99%D7%98%D7%9C%D7%99%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -4274,6 +4700,11 @@
           <t>https://he.wikipedia.org/wiki/איחוד_גרמניה</t>
         </is>
       </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%99%D7%97%D7%95%D7%93_%D7%92%D7%A8%D7%9E%D7%A0%D7%99%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -4301,6 +4732,11 @@
           <t>https://he.wikipedia.org/wiki/איחוד_גרמניה</t>
         </is>
       </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%99%D7%97%D7%95%D7%93_%D7%92%D7%A8%D7%9E%D7%A0%D7%99%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -4328,6 +4764,11 @@
           <t>https://he.wikipedia.org/wiki/אנטישמיות</t>
         </is>
       </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%A0%D7%98%D7%99%D7%A9%D7%9E%D7%99%D7%95%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -4355,6 +4796,11 @@
           <t>https://he.wikipedia.org/wiki/אנטישמיות</t>
         </is>
       </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%A0%D7%98%D7%99%D7%A9%D7%9E%D7%99%D7%95%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -4382,6 +4828,11 @@
           <t>https://he.wikipedia.org/wiki/פרשת_דרייפוס</t>
         </is>
       </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A4%D7%A8%D7%A9%D7%AA_%D7%93%D7%A8%D7%99%D7%99%D7%A4%D7%95%D7%A1</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -4409,6 +4860,11 @@
           <t>https://he.wikipedia.org/wiki/חיבת_ציון</t>
         </is>
       </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%97%D7%99%D7%91%D7%AA_%D7%A6%D7%99%D7%95%D7%9F</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -4433,7 +4889,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://he.wikipedia.org/wiki/חיבת_ציון</t>
+          <t>https://he.wikipedia.org/wiki/אחד_העם</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%97%D7%93_%D7%94%D7%A2%D7%9D</t>
         </is>
       </c>
     </row>
@@ -4463,6 +4924,11 @@
           <t>https://he.wikipedia.org/wiki/ההסתדרות_הציונית</t>
         </is>
       </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%94%D7%A1%D7%AA%D7%93%D7%A8%D7%95%D7%AA_%D7%94%D7%A6%D7%99%D7%95%D7%A0%D7%99%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -4490,6 +4956,11 @@
           <t>https://he.wikipedia.org/wiki/בנימין_זאב_הרצל</t>
         </is>
       </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%91%D7%A0%D7%99%D7%9E%D7%99%D7%9F_%D7%96%D7%90%D7%91_%D7%94%D7%A8%D7%A6%D7%9C</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4517,6 +4988,11 @@
           <t>https://he.wikipedia.org/wiki/תוכנית_אוגנדה</t>
         </is>
       </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%AA%D7%95%D7%9B%D7%A0%D7%99%D7%AA_%D7%90%D7%95%D7%92%D7%A0%D7%93%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -4544,6 +5020,11 @@
           <t>https://he.wikipedia.org/wiki/ציונות</t>
         </is>
       </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A6%D7%99%D7%95%D7%A0%D7%95%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -4571,6 +5052,11 @@
           <t>https://he.wikipedia.org/wiki/העלייה_הראשונה</t>
         </is>
       </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A2%D7%9C%D7%99%D7%99%D7%94_%D7%94%D7%A8%D7%90%D7%A9%D7%95%D7%A0%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -4598,6 +5084,11 @@
           <t>https://he.wikipedia.org/wiki/העלייה_הראשונה</t>
         </is>
       </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A2%D7%9C%D7%99%D7%99%D7%94_%D7%94%D7%A8%D7%90%D7%A9%D7%95%D7%A0%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -4625,6 +5116,11 @@
           <t>https://he.wikipedia.org/wiki/העלייה_השנייה</t>
         </is>
       </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A2%D7%9C%D7%99%D7%99%D7%94_%D7%94%D7%A9%D7%A0%D7%99%D7%99%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4652,6 +5148,11 @@
           <t>https://he.wikipedia.org/wiki/הקיבוץ</t>
         </is>
       </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A7%D7%99%D7%91%D7%95%D7%A5</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4679,6 +5180,11 @@
           <t>https://he.wikipedia.org/wiki/השומר</t>
         </is>
       </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A9%D7%95%D7%9E%D7%A8</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -4706,6 +5212,11 @@
           <t>https://he.wikipedia.org/wiki/אליעזר_בן_יהודה</t>
         </is>
       </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%9C%D7%99%D7%A2%D7%96%D7%A8_%D7%91%D7%9F_%D7%99%D7%94%D7%95%D7%93%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -4733,6 +5244,11 @@
           <t>https://he.wikipedia.org/wiki/אחוזת_בית</t>
         </is>
       </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%97%D7%95%D7%96%D7%AA_%D7%91%D7%99%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -4760,6 +5276,11 @@
           <t>https://he.wikipedia.org/wiki/ניל"י</t>
         </is>
       </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A0%D7%99%D7%9C%22%D7%99</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -4787,6 +5308,11 @@
           <t>https://he.wikipedia.org/wiki/פומפיוס</t>
         </is>
       </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A4%D7%95%D7%9E%D7%A4%D7%99%D7%95%D7%A1</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -4814,6 +5340,11 @@
           <t>https://he.wikipedia.org/wiki/הורדוס</t>
         </is>
       </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%95%D7%A8%D7%93%D7%95%D7%A1</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -4841,6 +5372,11 @@
           <t>https://he.wikipedia.org/wiki/הורדוס</t>
         </is>
       </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%95%D7%A8%D7%93%D7%95%D7%A1</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -4868,6 +5404,11 @@
           <t>https://he.wikipedia.org/wiki/הורדוס</t>
         </is>
       </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%95%D7%A8%D7%93%D7%95%D7%A1</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -4895,6 +5436,11 @@
           <t>https://he.wikipedia.org/wiki/המרד_הגדול</t>
         </is>
       </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A8%D7%93_%D7%94%D7%92%D7%93%D7%95%D7%9C</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -4922,6 +5468,11 @@
           <t>https://he.wikipedia.org/wiki/החשמונאים</t>
         </is>
       </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%97%D7%A9%D7%9E%D7%95%D7%A0%D7%90%D7%99%D7%9D</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -4949,6 +5500,11 @@
           <t>https://he.wikipedia.org/wiki/החשמונאים</t>
         </is>
       </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%97%D7%A9%D7%9E%D7%95%D7%A0%D7%90%D7%99%D7%9D</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -4976,6 +5532,11 @@
           <t>https://he.wikipedia.org/wiki/האיסיים</t>
         </is>
       </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%90%D7%99%D7%A1%D7%99%D7%99%D7%9D</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -5003,6 +5564,11 @@
           <t>https://he.wikipedia.org/wiki/המרד_הגדול</t>
         </is>
       </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A8%D7%93_%D7%94%D7%92%D7%93%D7%95%D7%9C</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -5030,6 +5596,11 @@
           <t>https://he.wikipedia.org/wiki/יבנה</t>
         </is>
       </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%99%D7%91%D7%A0%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -5057,6 +5628,11 @@
           <t>https://he.wikipedia.org/wiki/הסנהדרין</t>
         </is>
       </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A1%D7%A0%D7%94%D7%93%D7%A8%D7%99%D7%9F</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -5084,6 +5660,11 @@
           <t>https://he.wikipedia.org/wiki/יהודה_הנשיא</t>
         </is>
       </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%99%D7%94%D7%95%D7%93%D7%94_%D7%94%D7%A0%D7%A9%D7%99%D7%90</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -5111,6 +5692,11 @@
           <t>https://he.wikipedia.org/wiki/הח'ליפות_העבאסית</t>
         </is>
       </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%97%27%D7%9C%D7%99%D7%A4%D7%95%D7%AA_%D7%94%D7%A2%D7%91%D7%90%D7%A1%D7%99%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -5138,6 +5724,11 @@
           <t>https://he.wikipedia.org/wiki/בגדאד</t>
         </is>
       </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%91%D7%92%D7%93%D7%90%D7%93</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -5165,6 +5756,11 @@
           <t>https://he.wikipedia.org/wiki/בית_החוכמה</t>
         </is>
       </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%91%D7%99%D7%AA_%D7%94%D7%97%D7%95%D7%9B%D7%9E%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -5192,6 +5788,11 @@
           <t>https://he.wikipedia.org/wiki/ד'ימי</t>
         </is>
       </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%93%27%D7%99%D7%9E%D7%99</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -5219,6 +5820,11 @@
           <t>https://he.wikipedia.org/wiki/תנאי_עומר</t>
         </is>
       </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%AA%D7%A0%D7%90%D7%99_%D7%A2%D7%95%D7%9E%D7%A8</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -5246,6 +5852,11 @@
           <t>https://he.wikipedia.org/wiki/ריש_גלותא</t>
         </is>
       </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A8%D7%99%D7%A9_%D7%92%D7%9C%D7%95%D7%AA%D7%90</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -5273,6 +5884,11 @@
           <t>https://he.wikipedia.org/wiki/הגאונים</t>
         </is>
       </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%92%D7%90%D7%95%D7%A0%D7%99%D7%9D</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -5300,6 +5916,11 @@
           <t>https://he.wikipedia.org/wiki/סעדיה_גאון</t>
         </is>
       </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A1%D7%A2%D7%93%D7%99%D7%94_%D7%92%D7%90%D7%95%D7%9F</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -5327,6 +5948,11 @@
           <t>https://he.wikipedia.org/wiki/יהדות_אשכנז</t>
         </is>
       </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%99%D7%94%D7%93%D7%95%D7%AA_%D7%90%D7%A9%D7%9B%D7%A0%D7%96</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -5354,6 +5980,11 @@
           <t>https://he.wikipedia.org/wiki/רבנו_גרשום</t>
         </is>
       </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A8%D7%91%D7%A0%D7%95_%D7%92%D7%A8%D7%A9%D7%95%D7%9D</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -5381,6 +6012,11 @@
           <t>https://he.wikipedia.org/wiki/גזירות_תתנ"ו</t>
         </is>
       </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%92%D7%96%D7%99%D7%A8%D7%95%D7%AA_%D7%AA%D7%AA%D7%A0%22%D7%95</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -5408,6 +6044,11 @@
           <t>https://he.wikipedia.org/wiki/גרמניה_הנאצית</t>
         </is>
       </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%92%D7%A8%D7%9E%D7%A0%D7%99%D7%94_%D7%94%D7%A0%D7%90%D7%A6%D7%99%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -5435,6 +6076,11 @@
           <t>https://he.wikipedia.org/wiki/גרמניה_הנאצית</t>
         </is>
       </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%92%D7%A8%D7%9E%D7%A0%D7%99%D7%94_%D7%94%D7%A0%D7%90%D7%A6%D7%99%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -5462,6 +6108,11 @@
           <t>https://he.wikipedia.org/wiki/אדולף_היטלר</t>
         </is>
       </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%93%D7%95%D7%9C%D7%A3_%D7%94%D7%99%D7%98%D7%9C%D7%A8</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -5489,6 +6140,11 @@
           <t>https://he.wikipedia.org/wiki/חוקי_נירנברג</t>
         </is>
       </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%97%D7%95%D7%A7%D7%99_%D7%A0%D7%99%D7%A8%D7%A0%D7%91%D7%A8%D7%92</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -5516,6 +6172,11 @@
           <t>https://he.wikipedia.org/wiki/חוקי_נירנברג</t>
         </is>
       </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%97%D7%95%D7%A7%D7%99_%D7%A0%D7%99%D7%A8%D7%A0%D7%91%D7%A8%D7%92</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -5543,6 +6204,11 @@
           <t>https://he.wikipedia.org/wiki/ליל_הבדולח</t>
         </is>
       </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9C%D7%99%D7%9C_%D7%94%D7%91%D7%93%D7%95%D7%9C%D7%97</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -5570,11 +6236,16 @@
           <t>https://he.wikipedia.org/wiki/מלחמת_העולם_השנייה</t>
         </is>
       </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%9C%D7%97%D7%9E%D7%AA_%D7%94%D7%A2%D7%95%D7%9C%D7%9D_%D7%94%D7%A9%D7%A0%D7%99%D7%99%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>מלחמת העולם השנייה</t>
+          <t>שואה</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -5595,13 +6266,18 @@
       <c r="E135" s="2" t="inlineStr">
         <is>
           <t>https://he.wikipedia.org/wiki/קרב_סטלינגרד</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A7%D7%A8%D7%91_%D7%A1%D7%98%D7%9C%D7%99%D7%A0%D7%92%D7%A8%D7%93</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>מלחמת העולם השנייה</t>
+          <t>שואה</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -5622,13 +6298,18 @@
       <c r="E136" s="2" t="inlineStr">
         <is>
           <t>https://he.wikipedia.org/wiki/מלחמת_העולם_השנייה</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%9C%D7%97%D7%9E%D7%AA_%D7%94%D7%A2%D7%95%D7%9C%D7%9D_%D7%94%D7%A9%D7%A0%D7%99%D7%99%D7%94</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>מלחמת העולם השנייה</t>
+          <t>שואה</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -5649,6 +6330,11 @@
       <c r="E137" s="2" t="inlineStr">
         <is>
           <t>https://he.wikipedia.org/wiki/מלחמת_העולם_השנייה</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%9C%D7%97%D7%9E%D7%AA_%D7%94%D7%A2%D7%95%D7%9C%D7%9D_%D7%94%D7%A9%D7%A0%D7%99%D7%99%D7%94</t>
         </is>
       </c>
     </row>
@@ -5678,6 +6364,11 @@
           <t>https://he.wikipedia.org/wiki/הפתרון_הסופי</t>
         </is>
       </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A4%D7%AA%D7%A8%D7%95%D7%9F_%D7%94%D7%A1%D7%95%D7%A4%D7%99</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -5705,6 +6396,11 @@
           <t>https://he.wikipedia.org/wiki/ועידת_ואנזה</t>
         </is>
       </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%95%D7%A2%D7%99%D7%93%D7%AA_%D7%95%D7%90%D7%A0%D7%96%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -5729,7 +6425,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://he.wikipedia.org/wiki/אקציה</t>
+          <t>https://he.wikipedia.org/wiki/איינזצגרופן</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%99%D7%99%D7%A0%D7%96%D7%A6%D7%92%D7%A8%D7%95%D7%A4%D7%9F</t>
         </is>
       </c>
     </row>
@@ -5759,6 +6460,11 @@
           <t>https://he.wikipedia.org/wiki/אושוויץ</t>
         </is>
       </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%95%D7%A9%D7%95%D7%95%D7%99%D7%A5</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -5786,6 +6492,11 @@
           <t>https://he.wikipedia.org/wiki/מרד_גטו_ורשה</t>
         </is>
       </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%A8%D7%93_%D7%92%D7%98%D7%95_%D7%95%D7%A8%D7%A9%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -5810,7 +6521,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://he.wikipedia.org/wiki/השואה</t>
+          <t>https://he.wikipedia.org/wiki/יהדות_צפון_אפריקה_במלחמת_העולם_השנייה</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%99%D7%94%D7%93%D7%95%D7%AA_%D7%A6%D7%A4%D7%95%D7%9F_%D7%90%D7%A4%D7%A8%D7%99%D7%A7%D7%94_%D7%91%D7%9E%D7%9C%D7%97%D7%9E%D7%AA_%D7%94%D7%A2%D7%95%D7%9C%D7%9D_%D7%94%D7%A9%D7%A0%D7%99%D7%99%D7%94</t>
         </is>
       </c>
     </row>
@@ -5840,6 +6556,11 @@
           <t>https://he.wikipedia.org/wiki/המנדט_הבריטי</t>
         </is>
       </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A0%D7%93%D7%98_%D7%94%D7%91%D7%A8%D7%99%D7%98%D7%99</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -5867,6 +6588,11 @@
           <t>https://he.wikipedia.org/wiki/הספר_הלבן_(1939)</t>
         </is>
       </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A1%D7%A4%D7%A8_%D7%94%D7%9C%D7%91%D7%9F_%281939%29</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -5894,6 +6620,11 @@
           <t>https://he.wikipedia.org/wiki/המנדט_הבריטי</t>
         </is>
       </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A0%D7%93%D7%98_%D7%94%D7%91%D7%A8%D7%99%D7%98%D7%99</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -5921,6 +6652,11 @@
           <t>https://he.wikipedia.org/wiki/תנועת_המרי_העברי</t>
         </is>
       </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%AA%D7%A0%D7%95%D7%A2%D7%AA_%D7%94%D7%9E%D7%A8%D7%99_%D7%94%D7%A2%D7%91%D7%A8%D7%99</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -5948,6 +6684,11 @@
           <t>https://he.wikipedia.org/wiki/תנועת_המרי_העברי</t>
         </is>
       </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%AA%D7%A0%D7%95%D7%A2%D7%AA_%D7%94%D7%9E%D7%A8%D7%99_%D7%94%D7%A2%D7%91%D7%A8%D7%99</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -5975,6 +6716,11 @@
           <t>https://he.wikipedia.org/wiki/תוכנית_החלוקה</t>
         </is>
       </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%AA%D7%95%D7%9B%D7%A0%D7%99%D7%AA_%D7%94%D7%97%D7%9C%D7%95%D7%A7%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -6002,6 +6748,11 @@
           <t>https://he.wikipedia.org/wiki/תוכנית_החלוקה</t>
         </is>
       </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%AA%D7%95%D7%9B%D7%A0%D7%99%D7%AA_%D7%94%D7%97%D7%9C%D7%95%D7%A7%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -6029,6 +6780,11 @@
           <t>https://he.wikipedia.org/wiki/מלחמת_העצמאות</t>
         </is>
       </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%9C%D7%97%D7%9E%D7%AA_%D7%94%D7%A2%D7%A6%D7%9E%D7%90%D7%95%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -6056,6 +6812,11 @@
           <t>https://he.wikipedia.org/wiki/מגילת_העצמאות</t>
         </is>
       </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%92%D7%99%D7%9C%D7%AA_%D7%94%D7%A2%D7%A6%D7%9E%D7%90%D7%95%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -6083,6 +6844,11 @@
           <t>https://he.wikipedia.org/wiki/דוד_בן-גוריון</t>
         </is>
       </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%93%D7%95%D7%93_%D7%91%D7%9F-%D7%92%D7%95%D7%A8%D7%99%D7%95%D7%9F</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -6110,6 +6876,11 @@
           <t>https://he.wikipedia.org/wiki/העלייה_ההמונית</t>
         </is>
       </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A2%D7%9C%D7%99%D7%99%D7%94_%D7%94%D7%94%D7%9E%D7%95%D7%A0%D7%99%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -6137,6 +6908,11 @@
           <t>https://he.wikipedia.org/wiki/מעברה</t>
         </is>
       </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%A2%D7%91%D7%A8%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -6164,6 +6940,11 @@
           <t>https://he.wikipedia.org/wiki/חוק_השבות</t>
         </is>
       </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%97%D7%95%D7%A7_%D7%94%D7%A9%D7%91%D7%95%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -6191,6 +6972,11 @@
           <t>https://he.wikipedia.org/wiki/מדינת_ישראל</t>
         </is>
       </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%93%D7%99%D7%A0%D7%AA_%D7%99%D7%A9%D7%A8%D7%90%D7%9C</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -6218,6 +7004,11 @@
           <t>https://he.wikipedia.org/wiki/מדינת_לאום</t>
         </is>
       </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%93%D7%99%D7%A0%D7%AA_%D7%9C%D7%90%D7%95%D7%9D</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -6245,6 +7036,11 @@
           <t>https://he.wikipedia.org/wiki/מדינת_היהודים</t>
         </is>
       </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%93%D7%99%D7%A0%D7%AA_%D7%94%D7%99%D7%94%D7%95%D7%93%D7%99%D7%9D</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -6272,6 +7068,11 @@
           <t>https://he.wikipedia.org/wiki/הקונגרס_הציוני_העולמי_הראשון</t>
         </is>
       </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A7%D7%95%D7%A0%D7%92%D7%A8%D7%A1_%D7%94%D7%A6%D7%99%D7%95%D7%A0%D7%99_%D7%94%D7%A2%D7%95%D7%9C%D7%9E%D7%99_%D7%94%D7%A8%D7%90%D7%A9%D7%95%D7%9F</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -6299,6 +7100,11 @@
           <t>https://he.wikipedia.org/wiki/תנועת_ההשכלה_היהודית</t>
         </is>
       </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%AA%D7%A0%D7%95%D7%A2%D7%AA_%D7%94%D7%94%D7%A9%D7%9B%D7%9C%D7%94_%D7%94%D7%99%D7%94%D7%95%D7%93%D7%99%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -6326,6 +7132,11 @@
           <t>https://he.wikipedia.org/wiki/אנטישמיות</t>
         </is>
       </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%A0%D7%98%D7%99%D7%A9%D7%9E%D7%99%D7%95%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -6353,6 +7164,11 @@
           <t>https://he.wikipedia.org/wiki/בית_המקדש_השני</t>
         </is>
       </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%91%D7%99%D7%AA_%D7%94%D7%9E%D7%A7%D7%93%D7%A9_%D7%94%D7%A9%D7%A0%D7%99</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -6380,6 +7196,11 @@
           <t>https://he.wikipedia.org/wiki/רבן_יוחנן_בן_זכאי</t>
         </is>
       </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A8%D7%91%D7%9F_%D7%99%D7%95%D7%97%D7%A0%D7%9F_%D7%91%D7%9F_%D7%96%D7%9B%D7%90%D7%99</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -6407,6 +7228,11 @@
           <t>https://he.wikipedia.org/wiki/המרד_הגדול</t>
         </is>
       </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A8%D7%93_%D7%94%D7%92%D7%93%D7%95%D7%9C</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -6434,6 +7260,11 @@
           <t>https://he.wikipedia.org/wiki/יהדות_אשכנז</t>
         </is>
       </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%99%D7%94%D7%93%D7%95%D7%AA_%D7%90%D7%A9%D7%9B%D7%A0%D7%96</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -6461,6 +7292,11 @@
           <t>https://he.wikipedia.org/wiki/יהדות_אשכנז</t>
         </is>
       </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%99%D7%94%D7%93%D7%95%D7%AA_%D7%90%D7%A9%D7%9B%D7%A0%D7%96</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -6488,6 +7324,11 @@
           <t>https://he.wikipedia.org/wiki/גטו_ורשה</t>
         </is>
       </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%92%D7%98%D7%95_%D7%95%D7%A8%D7%A9%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -6515,6 +7356,11 @@
           <t>https://he.wikipedia.org/wiki/יודנראט</t>
         </is>
       </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%99%D7%95%D7%93%D7%A0%D7%A8%D7%90%D7%98</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -6542,6 +7388,11 @@
           <t>https://he.wikipedia.org/wiki/מרד_גטו_ורשה</t>
         </is>
       </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%A8%D7%93_%D7%92%D7%98%D7%95_%D7%95%D7%A8%D7%A9%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -6569,6 +7420,11 @@
           <t>https://he.wikipedia.org/wiki/השואה</t>
         </is>
       </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A9%D7%95%D7%90%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -6596,6 +7452,11 @@
           <t>https://he.wikipedia.org/wiki/המפלגה_הנאצית</t>
         </is>
       </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A4%D7%9C%D7%92%D7%94_%D7%94%D7%A0%D7%90%D7%A6%D7%99%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -6623,6 +7484,11 @@
           <t>https://he.wikipedia.org/wiki/מבצע_יואב</t>
         </is>
       </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%91%D7%A6%D7%A2_%D7%99%D7%95%D7%90%D7%91</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -6650,6 +7516,11 @@
           <t>https://he.wikipedia.org/wiki/מלחמת_העצמאות</t>
         </is>
       </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%9C%D7%97%D7%9E%D7%AA_%D7%94%D7%A2%D7%A6%D7%9E%D7%90%D7%95%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -6677,6 +7548,11 @@
           <t>https://he.wikipedia.org/wiki/מדינת_ישראל</t>
         </is>
       </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%93%D7%99%D7%A0%D7%AA_%D7%99%D7%A9%D7%A8%D7%90%D7%9C</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -6704,6 +7580,11 @@
           <t>https://he.wikipedia.org/wiki/מדינת_ישראל</t>
         </is>
       </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%93%D7%99%D7%A0%D7%AA_%D7%99%D7%A9%D7%A8%D7%90%D7%9C</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -6728,7 +7609,12 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://he.wikipedia.org/wiki/מדינת_לאום</t>
+          <t>https://he.wikipedia.org/wiki/קונגרס_וינה</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A7%D7%95%D7%A0%D7%92%D7%A8%D7%A1_%D7%95%D7%99%D7%A0%D7%94</t>
         </is>
       </c>
     </row>
@@ -6758,6 +7644,11 @@
           <t>https://he.wikipedia.org/wiki/המהפכה_התעשייתית</t>
         </is>
       </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%94%D7%A4%D7%9B%D7%94_%D7%94%D7%AA%D7%A2%D7%A9%D7%99%D7%99%D7%AA%D7%99%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -6785,6 +7676,11 @@
           <t>https://he.wikipedia.org/wiki/העלייה_הראשונה</t>
         </is>
       </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A2%D7%9C%D7%99%D7%99%D7%94_%D7%94%D7%A8%D7%90%D7%A9%D7%95%D7%A0%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -6809,7 +7705,12 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://he.wikipedia.org/wiki/ההסתדרות_הציונית</t>
+          <t>https://he.wikipedia.org/wiki/חיים_וייצמן</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%97%D7%99%D7%99%D7%9D_%D7%95%D7%99%D7%99%D7%A6%D7%9E%D7%9F</t>
         </is>
       </c>
     </row>
@@ -6839,6 +7740,11 @@
           <t>https://he.wikipedia.org/wiki/החשמונאים</t>
         </is>
       </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%97%D7%A9%D7%9E%D7%95%D7%A0%D7%90%D7%99%D7%9D</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -6866,6 +7772,11 @@
           <t>https://he.wikipedia.org/wiki/המרד_הגדול</t>
         </is>
       </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A8%D7%93_%D7%94%D7%92%D7%93%D7%95%D7%9C</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -6893,6 +7804,11 @@
           <t>https://he.wikipedia.org/wiki/בגדאד</t>
         </is>
       </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%91%D7%92%D7%93%D7%90%D7%93</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -6920,6 +7836,11 @@
           <t>https://he.wikipedia.org/wiki/ד'ימי</t>
         </is>
       </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%93%27%D7%99%D7%9E%D7%99</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -6947,6 +7868,11 @@
           <t>https://he.wikipedia.org/wiki/הגאונים</t>
         </is>
       </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%92%D7%90%D7%95%D7%A0%D7%99%D7%9D</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -6974,6 +7900,11 @@
           <t>https://he.wikipedia.org/wiki/הפתרון_הסופי</t>
         </is>
       </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A4%D7%AA%D7%A8%D7%95%D7%9F_%D7%94%D7%A1%D7%95%D7%A4%D7%99</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -6998,7 +7929,12 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://he.wikipedia.org/wiki/אקציה</t>
+          <t>https://he.wikipedia.org/wiki/הפתרון_הסופי</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A4%D7%AA%D7%A8%D7%95%D7%9F_%D7%94%D7%A1%D7%95%D7%A4%D7%99</t>
         </is>
       </c>
     </row>
@@ -7025,14 +7961,19 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://he.wikipedia.org/wiki/השואה</t>
+          <t>https://he.wikipedia.org/wiki/חסידי_אומות_העולם</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%97%D7%A1%D7%99%D7%93%D7%99_%D7%90%D7%95%D7%9E%D7%95%D7%AA_%D7%94%D7%A2%D7%95%D7%9C%D7%9D</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>מלחמת העולם השנייה</t>
+          <t>שואה</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -7053,6 +7994,11 @@
       <c r="E189" s="2" t="inlineStr">
         <is>
           <t>https://he.wikipedia.org/wiki/מלחמת_העולם_השנייה</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%9C%D7%97%D7%9E%D7%AA_%D7%94%D7%A2%D7%95%D7%9C%D7%9D_%D7%94%D7%A9%D7%A0%D7%99%D7%99%D7%94</t>
         </is>
       </c>
     </row>
@@ -7079,14 +8025,19 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://he.wikipedia.org/wiki/תנועת_המרי_העברי</t>
+          <t>https://he.wikipedia.org/wiki/אקסודוס_(אונייה)</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%A7%D7%A1%D7%95%D7%93%D7%95%D7%A1_%28%D7%90%D7%95%D7%A0%D7%99%D7%99%D7%94%29</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>מלחמת העולם השנייה</t>
+          <t>שואה</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -7107,13 +8058,18 @@
       <c r="E191" s="2" t="inlineStr">
         <is>
           <t>https://he.wikipedia.org/wiki/מלחמת_העולם_השנייה</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%9C%D7%97%D7%9E%D7%AA_%D7%94%D7%A2%D7%95%D7%9C%D7%9D_%D7%94%D7%A9%D7%A0%D7%99%D7%99%D7%94</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>מלחמת העולם השנייה</t>
+          <t>שואה</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -7134,13 +8090,18 @@
       <c r="E192" s="2" t="inlineStr">
         <is>
           <t>https://he.wikipedia.org/wiki/מלחמת_העולם_השנייה</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%9C%D7%97%D7%9E%D7%AA_%D7%94%D7%A2%D7%95%D7%9C%D7%9D_%D7%94%D7%A9%D7%A0%D7%99%D7%99%D7%94</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>מלחמת העולם השנייה</t>
+          <t>שואה</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -7161,6 +8122,11 @@
       <c r="E193" s="2" t="inlineStr">
         <is>
           <t>https://he.wikipedia.org/wiki/מלחמת_העולם_השנייה</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%9C%D7%97%D7%9E%D7%AA_%D7%94%D7%A2%D7%95%D7%9C%D7%9D_%D7%94%D7%A9%D7%A0%D7%99%D7%99%D7%94</t>
         </is>
       </c>
     </row>
@@ -7190,6 +8156,11 @@
           <t>https://he.wikipedia.org/wiki/הורדוס</t>
         </is>
       </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%95%D7%A8%D7%93%D7%95%D7%A1</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -7217,6 +8188,11 @@
           <t>https://he.wikipedia.org/wiki/ציונות</t>
         </is>
       </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A6%D7%99%D7%95%D7%A0%D7%95%D7%AA</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -7244,6 +8220,11 @@
           <t>https://he.wikipedia.org/wiki/השואה</t>
         </is>
       </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A9%D7%95%D7%90%D7%94</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -7271,6 +8252,11 @@
           <t>https://he.wikipedia.org/wiki/תנועת_המרי_העברי</t>
         </is>
       </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%AA%D7%A0%D7%95%D7%A2%D7%AA_%D7%94%D7%9E%D7%A8%D7%99_%D7%94%D7%A2%D7%91%D7%A8%D7%99</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -7298,6 +8284,11 @@
           <t>https://he.wikipedia.org/wiki/מדינת_ישראל</t>
         </is>
       </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%93%D7%99%D7%A0%D7%AA_%D7%99%D7%A9%D7%A8%D7%90%D7%9C</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -7325,6 +8316,11 @@
           <t>https://he.wikipedia.org/wiki/החשמונאים</t>
         </is>
       </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%97%D7%A9%D7%9E%D7%95%D7%A0%D7%90%D7%99%D7%9D</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -7350,6 +8346,3307 @@
       <c r="E200" s="2" t="inlineStr">
         <is>
           <t>https://he.wikipedia.org/wiki/החשמונאים</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%97%D7%A9%D7%9E%D7%95%D7%A0%D7%90%D7%99%D7%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>הסדר השמרני</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>עקרונות ההסדר של ועידת וינה</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>ועידת וינה התבססה על שלושה עקרונות: לגיטימיות (השבת השושלות ה'חוקיות' שהודחו), פיצוי המעצמות המנצחות בשטחים, ואיזון כוחות שימנע הגמוניה של מעצמה אחת. ההסדר עיצב את מפת אירופה לדורות, אך מתוך התעלמות מהשאיפות הלאומיות והליברליות שהתסיסה תפרוץ בהמשך.</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/קונגרס_וינה</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A7%D7%95%D7%A0%D7%92%D7%A8%D7%A1_%D7%95%D7%99%D7%A0%D7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>המהפכה הצרפתית</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>הכרזת זכויות האדם והאזרח</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>אחד ההישגים המכוננים של המהפכה הצרפתית היה 'הכרזת זכויות האדם והאזרח' (1789), שקבעה כי בני האדם נולדים חופשיים ושווים בזכויותיהם, וכי הריבונות שייכת לאומה. ההכרזה ביטאה את רעיונות הנאורות והפכה למקור השראה לתנועות לאומיות וליברליות באירופה.</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/המהפכה_הצרפתית</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%94%D7%A4%D7%9B%D7%94_%D7%94%D7%A6%D7%A8%D7%A4%D7%AA%D7%99%D7%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>נפוליאון</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>הקוד הנפוליאוני והפצת רעיונות המהפכה</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>נפוליאון הנהיג את 'הקוד האזרחי' (קוד נפוליאון) שעיגן שוויון בפני החוק, חופש דת והגנה על הקניין, וביטל שרידי פיאודליזם. במסעותיו הפיץ עקרונות אלה ברחבי אירופה. כך, גם דרך הכיבוש, תרמה צרפת הנפוליאונית להתפשטות הרעיונות שעליהם נשענו התנועות הלאומיות.</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/נפוליאון_בונפרטה</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A0%D7%A4%D7%95%D7%9C%D7%99%D7%90%D7%95%D7%9F_%D7%91%D7%95%D7%A0%D7%A4%D7%A8%D7%98%D7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>ליברליזם</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>עקרונות הליברליזם הקלאסי</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>הליברליזם הקלאסי דגל בחירויות הפרט (ביטוי, דת, קניין), בשוויון בפני החוק, בשלטון מוגבל באמצעות חוקה והפרדת רשויות, ובכלכלת שוק. במאה ה-19 שולבו ערכים אלה פעמים רבות עם הדרישה הלאומית לעצמאות, ושני הזרמים יחד אתגרו את הסדר השמרני.</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/ליברליזם</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9C%D7%99%D7%91%D7%A8%D7%9C%D7%99%D7%96%D7%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>איחוד איטליה</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>גריבלדי ו'מסע האלף'</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>ג'וזפה גריבלדי, מנהיג מהפכני כריזמטי, הוביל ב-1860 את 'מסע האלף' (האדומים) – כיבוש סיציליה ודרום איטליה בכוח מתנדבים. הוא מסר את השטחים שכבש לידי מלך פיימונטה, ובכך תרם תרומה מכרעת לאיחוד איטליה תחת שלטון מלוכני אחד.</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/איחוד_איטליה</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%99%D7%97%D7%95%D7%93_%D7%90%D7%99%D7%98%D7%9C%D7%99%D7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>פרשת דרייפוס</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>שני המחנות בחברה הצרפתית</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>פרשת דרייפוס פילגה את צרפת לשני מחנות: ה'דרייפוסרים' (תומכי זיכוי, ובהם הסופר אמיל זולא במאמרו 'אני מאשים'), שדגלו באמת, צדק וזכויות אדם, וה'אנטי-דרייפוסרים' (לאומנים, כנסייה וצבא), שהציבו את 'כבוד הצבא והאומה' מעל הצדק. הפרשה חשפה את עומק האנטישמיות גם בחברה רפובליקנית.</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/פרשת_דרייפוס</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A4%D7%A8%D7%A9%D7%AA_%D7%93%D7%A8%D7%99%D7%99%D7%A4%D7%95%D7%A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>השכלה ואמנציפציה</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>ראשית ההשכלה היהודית – מנדלסון</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>תנועת ההשכלה היהודית ראשיתה בברלין במאה ה-18, ומשה מנדלסון נחשב לאבי המשכילים. המשכילים קראו לשילוב לימודי חול ושפת המדינה לצד היהדות, לתיקון החברה היהודית ולהשתלבות. ההשכלה הניחה תשתית הן להתבוללות והן, בהמשך, ללאומיות היהודית המודרנית.</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/תנועת_ההשכלה_היהודית</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%AA%D7%A0%D7%95%D7%A2%D7%AA_%D7%94%D7%94%D7%A9%D7%9B%D7%9C%D7%94_%D7%94%D7%99%D7%94%D7%95%D7%93%D7%99%D7%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>מבשרי הציונות</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>אחד העם והוויכוח עם הציונות המדינית</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>אחד העם מתח ביקורת חריפה על הציונות המדינית של הרצל: לטענתו היא שמה דגש מופרז על פעולה דיפלומטית ועל פתרון מצוקת היהודים, והזניחה את ה'צרת היהדות' – משבר הזהות והתרבות. הוא קרא קודם כול לבניין 'מרכז רוחני' איכותי בארץ ישראל שיחייה את התרבות הלאומית.</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/אחד_העם</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%97%D7%93_%D7%94%D7%A2%D7%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>ארגוני העבודה</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>גדוד העבודה</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>גדוד העבודה (נוסד 1920, על שם יוסף טרומפלדור) היה מסגרת שיתופית של פועלים מאנשי העלייה השלישית, שעסקה בסלילת כבישים, בבנייה ובהתיישבות. הגדוד דגל בקומונה ארצית גדולה ובשוויון מלא, ותרם להתפתחות ההתיישבות העובדת, אך התפלג בשל מחלוקות אידאולוגיות.</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/גדוד_העבודה</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%92%D7%93%D7%95%D7%93_%D7%94%D7%A2%D7%91%D7%95%D7%93%D7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>ההתיישבות העובדת</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>עקרונות הקיבוץ</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>הקיבוץ התבסס על עקרונות של שיתוף מלא בקניין ובצריכה, עבודה עצמית, שוויון, וקבלת החלטות דמוקרטית באסיפה הכללית. הוא שילב התיישבות חקלאית, ביטחון ואידאולוגיה סוציאליסטית-ציונית, והפך לאחד מסמלי ההגשמה החלוצית ולגורם מרכזי בבניין הארץ ובהגנתה.</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/הקיבוץ</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A7%D7%99%D7%91%D7%95%D7%A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>העיר העברית</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>צמיחת תל אביב לעיר עברית</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>תל אביב צמחה מן השכונה 'אחוזת בית' (1909) לעיר העברית הראשונה: היא התרחבה במהירות, פיתחה תכנון עירוני מודרני, מוסדות תרבות, חינוך וכלכלה עבריים, וקלטה גלי עלייה. העיר ייצגה את האלטרנטיבה העירונית-מודרנית להגשמה הציונית, לצד ההתיישבות החקלאית.</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/תל_אביב</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%AA%D7%9C_%D7%90%D7%91%D7%99%D7%91</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>מרד בר כוכבא</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>רקע ומהלך מרד בר כוכבא</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>מרד בר כוכבא (132–135 לספירה) פרץ בימי הקיסר אדריאנוס, על רקע גזירות (כנראה איסור מילה והקמת מושבה רומית בירושלים). שמעון בר כוכבא הנהיג את המרד, ורבים ראו בו דמות משיחית (ר' עקיבא תמך בו). המורדים הקימו שלטון עצמאי זמני, אך רומא דיכאה את המרד באכזריות.</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/מרד_בר_כוכבא</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%A8%D7%93_%D7%91%D7%A8_%D7%9B%D7%95%D7%9B%D7%91%D7%90</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>מרד בר כוכבא</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>תוצאות מרד בר כוכבא</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>דיכוי מרד בר כוכבא היה הרסני: הרג רב, חורבן יישובים (בעיקר ביהודה), מכירת שבויים לעבדות וגזירות דת ('גזירות השמד'). ירושלים הפכה למושבה רומית ('איליה קפיטולינה') והכניסה ליהודים נאסרה. מרכז החיים היהודיים עבר לגליל, והמרד סימן את סוף הניסיונות להחזיר עצמאות מדינית בכוח.</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/מרד_בר_כוכבא</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%A8%D7%93_%D7%91%D7%A8_%D7%9B%D7%95%D7%9B%D7%91%D7%90</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>הסנהדרין</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>מעבר הסנהדרין לגליל</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>לאחר דיכוי מרד בר כוכבא וגזירות השמד עבר מרכז ההנהגה היהודית לגליל. הסנהדרין נדדה בין יישובים (אושא, בית שערים, ציפורי, טבריה), ובראשה עמדה שושלת הנשיאים מבית הלל. בגליל המשיכה ההנהגה לפסוק הלכה, לעבר את לוח השנה ולשמר את האחדות הלאומית-דתית בלא ריבונות.</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/הסנהדרין</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A1%D7%A0%D7%94%D7%93%D7%A8%D7%99%D7%9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>בית המקדש</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>העלייה לרגל ומרכזיות ירושלים</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>בימי בית שני עלו יהודים מארץ ישראל ומהתפוצות לירושלים בשלושת הרגלים (פסח, שבועות, סוכות). העלייה לרגל חיזקה את מעמד ירושלים והמקדש כמרכז דתי ולאומי מאחד, חיזקה את הזיקה בין הקהילות, ותרמה לכלכלת העיר. חורבן המקדש קטע מסורת זו וחייב חלופות רוחניות.</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/בית_המקדש_השני</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%91%D7%99%D7%AA_%D7%94%D7%9E%D7%A7%D7%93%D7%A9_%D7%94%D7%A9%D7%A0%D7%99</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>יהדות אשכנז</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>לימוד התורה ובעלי התוספות</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>יהדות אשכנז פיתחה מרכזי תורה חשובים. לאחר רש"י, שפירושיו לתנ"ך ולתלמוד הפכו ליסוד, פעלו 'בעלי התוספות' (רבים מהם מצאצאיו ותלמידיו) שפיתחו שיטת לימוד תלמודית מעמיקה ופלפולית. הלמדנות האשכנזית ביססה את מעמדה הרוחני של הקהילה והשפיעה על לימוד התורה לדורות.</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/יהדות_אשכנז</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%99%D7%94%D7%93%D7%95%D7%AA_%D7%90%D7%A9%D7%9B%D7%A0%D7%96</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>מעמד היהודים</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>השוואת מעמד היהודים: אסלאם מול נצרות</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>מעמד היהודים תחת האסלאם (ד'ימי) היה לרוב יציב ומוסדר יותר – חלק ממערכת כוללת של בני חסות, עם שגשוג כלכלי ותרבותי. תחת הנצרות באירופה היה מעמדם פגיע יותר, נע בין חסות שליטים לפרעות וגירושים, ולווה בעוינות דתית עזה. ההשוואה מחדדת את תלות הקיום היהודי בתנאי הסביבה.</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/ד'ימי</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%93%27%D7%99%D7%9E%D7%99</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>שואה</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>הגטאות</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>ארכיון 'עונג שבת' בגטו ורשה</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>בגטו ורשה פעלה מחתרת תיעוד בשם 'עונג שבת', בהובלת ההיסטוריון עמנואל רינגלבלום, שאספה מסמכים, יומנים ועדויות כדי לתעד את חיי הגטו ואת גורל היהודים. הארכיון, שנטמן בקופסאות חלב ונחשף לאחר המלחמה, הוא ביטוי מובהק להתנגדות רוחנית ולשאיפה שהאמת תישמר ותיוודע.</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/גטו_ורשה</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%92%D7%98%D7%95_%D7%95%D7%A8%D7%A9%D7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>שואה</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>מחנות ההשמדה</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>הסלקציה באושוויץ</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>עם הגעת הרכבות לאושוויץ-בירקנאו נערכה 'סלקציה': קצינים נאצים מיינו את המגיעים – רובם נשלחו מיד אל תאי הגזים, ומיעוט שנמצא כשיר נשלח לעבודת פרך בתנאים קטלניים. הסלקציה מגלמת את אופייה התעשייתי והשיטתי של ההשמדה ואת הפיכת הרצח למנגנון מאורגן.</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/אושוויץ</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%95%D7%A9%D7%95%D7%95%D7%99%D7%A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>שואה</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>הפתרון הסופי</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>מבצע ריינהרד ומחנות ההשמדה בפולין</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>במסגרת 'מבצע ריינהרד' (1942–1943) הוקמו בפולין הכבושה מחנות ההשמדה בלז'ץ, סוביבור וטרבלינקה, שתוכננו לרצח מיידי וכמעט בלעדי של יהודי 'הגנרלגוברנמן'. במחנות אלה נרצחו בתאי גזים מאות אלפי יהודים בזמן קצר. הם מסמנים את שיא ההשמדה השיטתית של 'הפתרון הסופי'.</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/הפתרון_הסופי</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A4%D7%AA%D7%A8%D7%95%D7%9F_%D7%94%D7%A1%D7%95%D7%A4%D7%99</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>שואה</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>מדיניות אנטי-יהודית</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>החרפת המדיניות עם פרוץ המלחמה</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>עם כיבוש פולין (1939) עברה המדיניות הנאצית הסלמה: ריכוז מיליוני יהודים תחת שליטה, סימון (טלאי צהוב), עבודות כפייה, החרמת רכוש וריכוז בגטאות. המעבר משטח גרמניה אל מזרח אירופה, בעל ריכוז היהודים הגדול, הפך את 'שאלת היהודים' בעיני הנאצים לבעיה בקנה מידה אחר – בדרך אל ההשמדה.</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/השואה</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A9%D7%95%D7%90%D7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>המנדט הבריטי</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>מאורעות 1936–1939 (המרד הערבי)</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>בשנים 1936–1939 פרץ 'המרד הערבי' נגד השלטון הבריטי ונגד היישוב היהודי – שביתות, מתקפות והתפרעויות. היישוב הגיב במדיניות 'הבלגה', בחיזוק ההגנה ובהתיישבות 'חומה ומגדל'. המאורעות הביאו את בריטניה לוועדת פיל (שהציעה חלוקה) ובהמשך ל'ספר הלבן' 1939 שצימצם את העלייה.</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/המנדט_הבריטי</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A0%D7%93%D7%98_%D7%94%D7%91%D7%A8%D7%99%D7%98%D7%99</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>ההכרעה הבינלאומית</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>גבולות המדינה בתוכנית החלוקה</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>תוכנית החלוקה (1947) הקצתה למדינה היהודית שטח מקוטע משלושה אזורים (מישור החוף, עמק יזרעאל והגליל המזרחי, והנגב), למדינה הערבית שטח נפרד, ולירושלים מעמד בינלאומי מיוחד. המבנה המקוטע והקושי להגן עליו היו בין השיקולים, אך ההנהגה הציונית קיבלה את התוכנית כבסיס למדינה.</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/תוכנית_החלוקה</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%AA%D7%95%D7%9B%D7%A0%D7%99%D7%AA_%D7%94%D7%97%D7%9C%D7%95%D7%A7%D7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>מלחמת העצמאות</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>פלישת צבאות ערב</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>מיד עם הכרזת המדינה (14 במאי 1948) פלשו צבאותיהן של מצרים, ירדן, סוריה, לבנון ועיראק לשטח ישראל, בכוונה למנוע את קיומה. צה"ל, שזה עתה הוקם, בלם את הפלישה בקרבות קשים ועבר בהמשך למתקפות נגד. ההתמודדות מול חמש מדינות ערב סימנה את אופי המלחמה הקיומי.</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/מלחמת_העצמאות</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%9C%D7%97%D7%9E%D7%AA_%D7%94%D7%A2%D7%A6%D7%9E%D7%90%D7%95%D7%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>סוגיות נבחרות</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>קליטת עלייה</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>מבצעי העלאת קהילות שלמות</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>במסגרת העלייה ההמונית בוצעו מבצעי העלאה של קהילות שלמות, ובהם 'מרבד הקסמים' (העלאת יהודי תימן, 1949–1950) ו'עזרא ונחמיה' (העלאת יהודי עיראק, 1950–1951). המבצעים, שכללו רכבת אווירית, חיסלו קהילות ותיקות בארצות האסלאם והעמידו את המדינה בפני אתגר קליטה עצום.</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/העלייה_ההמונית</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A2%D7%9C%D7%99%D7%99%D7%94_%D7%94%D7%94%D7%9E%D7%95%D7%A0%D7%99%D7%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>סוגיות נבחרות</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>קליטת עלייה</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>מן המעברות לשיכוני הקבע</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>בהדרגה פורקו המעברות, ותושביהן עברו לשיכוני קבע ולעיירות פיתוח שהוקמו ברחבי הארץ, רבות מהן בפריפריה. המעבר שיפר את תנאי הדיור אך לעיתים הנציח פערים גאוגרפיים-חברתיים בין מרכז לפריפריה, שהפכו לסוגיה מתמשכת בחברה הישראלית.</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/מעברה</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%A2%D7%91%D7%A8%D7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>הח'ליפות העבאסית</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>שיא הח'ליפות העבאסית ושקיעתה</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>הח'ליפות העבאסית הגיעה לשיאה במאות ה-8–9 (בימי הארון אל-רשיד ואל-מאמון) כמעצמה עשירה ומרכז תרבותי. בהמשך נחלשה: התפצלות פוליטית, עליית כוחות מקומיים וצבאיים, ולבסוף כיבוש בגדאד בידי המונגולים (1258). היחלשות זו השפיעה גם על מעמד מרכז יהדות בבל.</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/הח'ליפות_העבאסית</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%97%27%D7%9C%D7%99%D7%A4%D7%95%D7%AA_%D7%94%D7%A2%D7%91%D7%90%D7%A1%D7%99%D7%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>מרכז תרבותי</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>מדענים ותחומי ידע בבית החוכמה</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>בבית החוכמה ובעולם המוסלמי פעלו מדענים פורצי דרך: אל-ח'ואריזמי (אבי האלגברה והאלגוריתם), רופאים, אסטרונומים ופילוסופים. תורגמו ופותחו ידע יווני, פרסי והודי במתמטיקה, רפואה ואסטרונומיה. תרומה זו שימרה את המורשת הקלאסית והעבירה אותה בהמשך גם לאירופה.</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/בית_החוכמה</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%91%D7%99%D7%AA_%D7%94%D7%97%D7%95%D7%9B%D7%9E%D7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>מנהיגות רוחנית</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>סעדיה גאון וחיבור 'אמונות ודעות'</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>רב סעדיה גאון חיבר את 'אמונות ודעות' – מן החיבורים הראשונים של פילוסופיה יהודית שיטתית, שביקש ליישב בין התורה לבין התבונה. הוא נאבק בכת הקראים שדחתה את התורה שבעל פה, וביסס את סמכות ההלכה הרבנית. פועלו חיזק את אחדות העם סביב מרכז בבל.</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/סעדיה_גאון</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A1%D7%A2%D7%93%D7%99%D7%94_%D7%92%D7%90%D7%95%D7%9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>הנהגת יהדות בבל</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>היחס בין ראש הגולה לראשי הישיבות</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>הנהגת יהדות בבל התחלקה בין ראש הגולה (סמכות מדינית-ייצוגית מול השלטון) לבין ראשי הישיבות-הגאונים (סמכות רוחנית-הלכתית). בין שני המוקדים שררו לעיתים מתחים על סמכות ומעמד, אך שיתוף הפעולה ביניהם העניק ליהדות בבל הנהגה יציבה וכוללת לאורך דורות.</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/ריש_גלותא</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A8%D7%99%D7%A9_%D7%92%D7%9C%D7%95%D7%AA%D7%90</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>אביב העמים</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>הפרלמנט של פרנקפורט</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>במהלך אביב העמים (1848) התכנס בפרנקפורט פרלמנט גרמני נבחר, שביקש לאחד את המדינות הגרמניות תחת חוקה ליברלית ולהציע כתר קיסרי. הניסיון כשל – מלך פרוסיה סירב לכתר 'מידי העם', והפרלמנט התפרק. הכישלון לימד שאיחוד גרמניה יושג בכוח מדיני (ביסמרק) ולא בדרך פרלמנטרית-ליברלית.</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/אביב_העמים</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%91%D7%99%D7%91_%D7%94%D7%A2%D7%9E%D7%99%D7%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>גורמים לצמיחת הלאומיות</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>רכבות ותקשורת ככלי ללכידות לאומית</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>פיתוח הרכבות, הטלגרף והעיתונות במאה ה-19 קיצר מרחקים וחיבר אזורים ואוכלוסיות. אמצעים אלה אפשרו הפצה מהירה של רעיונות, יצירת 'מרחב ציבורי' ושפה משותפת, וחיזקו את תחושת ההשתייכות הלאומית החוצה גבולות מקומיים – תשתית מעשית להתגבשות הלאומיות.</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/המהפכה_התעשייתית</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%94%D7%A4%D7%9B%D7%94_%D7%94%D7%AA%D7%A2%D7%A9%D7%99%D7%99%D7%AA%D7%99%D7%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>התנועה הרומנטית</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>הרומנטיקה והתרבות הלאומית</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>התנועה הרומנטית טיפחה איסוף פולקלור, אגדות עם, שירה ומוזיקה לאומית, וחקר השפה וההיסטוריה של העם. יוצרים ואנשי רוח רומנטיים העניקו ללאום 'נשמה' ותודעת ייחוד תרבותי. כך סיפקה הרומנטיקה ללאומיות תוכן רגשי-תרבותי, מעבר לרעיון הפוליטי המופשט.</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/התנועה_הרומנטית</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%AA%D7%A0%D7%95%D7%A2%D7%94_%D7%94%D7%A8%D7%95%D7%9E%D7%A0%D7%98%D7%99%D7%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>הקונגרס הציוני</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>סמלי התנועה הציונית</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>הקונגרס הציוני הראשון עיצב סמלים לאומיים שליכדו את התנועה: הדגל (כחול-לבן עם מגן דוד), ההמנון ('התקווה'), והשקל כאמצעי חברות והצבעה. הסמלים העניקו לציונות מאפיינים של תנועה לאומית מאורגנת, וחיזקו את תחושת ההשתייכות והזהות המשותפת של חבריה.</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/הקונגרס_הציוני_העולמי_הראשון</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A7%D7%95%D7%A0%D7%92%D7%A8%D7%A1_%D7%94%D7%A6%D7%99%D7%95%D7%A0%D7%99_%D7%94%D7%A2%D7%95%D7%9C%D7%9E%D7%99_%D7%94%D7%A8%D7%90%D7%A9%D7%95%D7%9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>אנטישמיות מודרנית</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>אמנציפציה וכישלונה כרקע לציונות</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>במהלך המאה ה-19 זכו יהודים במדינות מערב אירופה ל'אמנציפציה' – שוויון זכויות אזרחי. רבים קיוו שההשתלבות תפתור את 'שאלת היהודים'. אולם התגברות האנטישמיות המודרנית (ובמיוחד פרשת דרייפוס) הוכיחה כי גם אמנציפציה אינה מבטיחה קבלה, ומסקנה זו דחפה אל הפתרון הלאומי-ציוני.</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/אנטישמיות</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%A0%D7%98%D7%99%D7%A9%D7%9E%D7%99%D7%95%D7%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>הכיבוש הרומי</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>פומפיוס והכניסה לקודש הקודשים</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>כאשר כבש פומפיוס את ירושלים (63 לפנה"ס), הוא נכנס לקודש הקודשים שבמקדש – מעשה שנתפס כחילול קודש וזעזע את היהודים. הוא לא בזז את אוצרות המקדש אך כפף את יהודה לרומא והפחית את שטחה. אירוע זה סימל את אובדן העצמאות ואת ראשית התלות והחיכוך עם השלטון הרומי.</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/פומפיוס</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A4%D7%95%D7%9E%D7%A4%D7%99%D7%95%D7%A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>הורדוס</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>בניית קיסריה והנמל</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>בין מפעלי הבנייה של הורדוס בלטה העיר קיסריה על חוף הים – עיר נמל הלניסטית מפוארת ובה מקדש לקיסר, תיאטרון ואמת מים. קיסריה שירתה את הכלכלה והמסחר וביטאה את נאמנותו של הורדוס לרומא ואת אופיו ההלניסטי של שלטונו, שעורר הסתייגות בקרב יהודים.</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/הורדוס</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%95%D7%A8%D7%93%D7%95%D7%A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>מירושלים ליבנה</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>תקנות יבנה וסדר התפילה</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>ביבנה תוקנו תקנות שעיצבו את הדת ללא מקדש: קביעת נוסח התפילה כתחליף לעבודת הקורבנות, תקנות 'זכר למקדש', וקביעת מועדים והלכות אחידות. תקנות אלה, לצד מרכזיות בית הכנסת ובית המדרש, אפשרו רצף וקיום של חיים יהודיים מלאים גם לאחר החורבן.</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/יבנה</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%99%D7%91%D7%A0%D7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>שואה</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>ביסוס המשטר הנאצי</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>התעמולה הנאצית</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>המשטר הנאצי הקים מנגנון תעמולה רב-עוצמה בראשות יוזף גבלס, ששלט בעיתונות, ברדיו, בקולנוע ובאספות המוניות. התעמולה האדירה את דמות המנהיג, הפיצה את האנטישמיות ואת תורת הגזע, וגייסה את הציבור למשטר. היא הייתה כלי מרכזי בעיצוב התודעה ובביסוס השלטון הטוטליטרי.</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/המפלגה_הנאצית</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A4%D7%9C%D7%92%D7%94_%D7%94%D7%A0%D7%90%D7%A6%D7%99%D7%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>שואה</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>הצלה והתנגדות</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>'הבריחה' של שארית הפליטה</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>לאחר המלחמה ארגנה תנועת 'הבריחה' את מעבריהם החשאיים של ניצולי שואה ממזרח אירופה אל מחנות העקורים ואל חופי הים, כתחנה בדרך להעפלה לארץ ישראל. התנועה, שפעלה בסיוע שליחים מהיישוב והבריגדה, ביטאה את שאיפת הניצולים לעזוב את 'בית הקברות' האירופי ולבנות חיים חדשים.</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/השואה</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A9%D7%95%D7%90%D7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>שואה</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>מבנה הכוחות</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>מעצמות הציר מול בעלות הברית</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>מלחמת העולם השנייה התנהלה בין שני גושים: 'מעצמות הציר' (גרמניה הנאצית, איטליה הפשיסטית ויפן) שחתרו להתפשטות ולשליטה, מול 'בעלות הברית' (בריטניה, ברית המועצות, ארצות הברית ועוד). העליונות במשאבים, בכוח אדם ובתעשייה של בעלות הברית הכריעה בסופו של דבר את המלחמה.</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/מלחמת_העולם_השנייה</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%9C%D7%97%D7%9E%D7%AA_%D7%94%D7%A2%D7%95%D7%9C%D7%9D_%D7%94%D7%A9%D7%A0%D7%99%D7%99%D7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>שלושת הנימוקים לזכות במגילת העצמאות</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>מגילת העצמאות ביססה את הזכות להקמת מדינה יהודית על שלושה נימוקים: הזיקה ההיסטורית-דתית של העם לארץ ישראל (ערש העם); ההכרה הבינלאומית (הצהרת בלפור והחלטת האו"ם); ולקח השואה, שהוכיח את הצורך החיוני במדינה ריבונית שתקלוט את העם ותגן עליו.</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/מגילת_העצמאות</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%92%D7%99%D7%9C%D7%AA_%D7%94%D7%A2%D7%A6%D7%9E%D7%90%D7%95%D7%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>סוגיות נבחרות</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>עיצוב המשטר</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>פרשת אלטלנה וריכוז הכוח הצבאי</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>פרשת אלטלנה (יוני 1948) – העימות סביב אוניית הנשק של האצ"ל – הסתיימה בהוראת בן-גוריון לירות על האונייה. האירוע, קשה ככל שהיה, ביסס עיקרון יסוד של ממלכתיות: צבא אחד (צה"ל) הכפוף לממשלה הנבחרת, ללא מסגרות מזוינות עצמאיות. כך התחזק מונופול המדינה על הכוח.</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/דוד_בן-גוריון</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%93%D7%95%D7%93_%D7%91%D7%9F-%D7%92%D7%95%D7%A8%D7%99%D7%95%D7%9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>הצהרת בלפור</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>הרקע לאימוץ הצהרת בלפור</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>הצהרת בלפור (1917) ניתנה משיקולים בריטיים כפולים: הצורך בתמיכת יהדות ארה"ב ורוסיה כדי לחזק את ברית המלחמה, וחשש שגרמניה תנצל את הציונות לטובתה תחילה. לחצו של חיים וייצמן ופעולות דיפלומטיות ממוקדות הפכו את ההזדמנות להכרזה פורמלית. האינטרס האסטרטגי הבריטי ונאמנות לציונות קלעו יחדיו.</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/הצהרת_בלפור</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A6%D7%94%D7%A8%D7%AA_%D7%91%D7%9C%D7%A4%D7%95%D7%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>הצהרת בלפור</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>תוכן הצהרת בלפור ומשמעותה</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>הצהרת בלפור (2 בנובמבר 1917) הכריזה כי ממשלת בריטניה 'מביטה בעין יפה' על הקמת 'בית לאומי' לעם היהודי בארץ ישראל, ובלבד שלא תיפגענה הזכויות האזרחיות-הדתיות של תושבים לא-יהודים. זו הייתה לראשונה הכרה בינלאומית-ממשלתית בשאיפות הציונות ואבן יסוד לחוקיות הבית הלאומי.</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/הצהרת_בלפור</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A6%D7%94%D7%A8%D7%AA_%D7%91%D7%9C%D7%A4%D7%95%D7%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>הצהרת בלפור</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>הסתירה הכפולה בהצהרת בלפור</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>הצהרת בלפור יצרה מחויבות כפולה וסותרת: הבטחת 'בית לאומי' לעם היהודי, לצד ערובה לאי-פגיעה בזכויות קיימות של 'הקהילות הלא-יהודיות'. כל צד – ציוני וערבי – פירש את ההצהרה לטובתו, ואי-הבהירות הפכה למקור מרכזי לסכסוך בתקופת המנדט ולמחלוקות פוליטיות חסרות-פתרון.</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/הצהרת_בלפור</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A6%D7%94%D7%A8%D7%AA_%D7%91%D7%9C%D7%A4%D7%95%D7%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>ועדת פיל</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>ועדת פיל 1937 – ראשית רעיון החלוקה</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>ועדת פיל (1937) הוקמה בעקבות המרד הערבי לחקר הסכסוך בארץ ישראל. ועדה זו הסיקה לראשונה כי המנדט אינו ניתן למימוש בו-זמנית לשני הצדדים, והמליצה על חלוקת הארץ לשתי מדינות – יהודית וערבית – עם אזור בריטי שיכלול את ירושלים. זו הייתה ראשית הגיבוש הרשמי של רעיון שתי המדינות.</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/ועדת_פיל</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%95%D7%A2%D7%93%D7%AA_%D7%A4%D7%99%D7%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>ועדת פיל</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>תגובות לתוכנית פיל</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>ההנהגה הציונית (בן-גוריון) קיבלה את עיקרון החלוקה כבסיס, אף שהשטח המוצע קטן, ראתה בו צעד ל'מדינה יהודית'. הערבים דחו מכול וכול. בריטניה עצמה נסוגה בוועדת וודהד (1938) ולא יישמה. עם זאת, ועדת פיל עיצבה את השאלה: לא 'האם' לחלק, אלא 'כיצד ואיפה' – ובאיזה גבולות.</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/ועדת_פיל</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%95%D7%A2%D7%93%D7%AA_%D7%A4%D7%99%D7%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>ועדת אנגלו-אמריקאית</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>ועדת החקירה האנגלו-אמריקאית 1946</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>לאחר המלחמה מינו בריטניה וארה"ב ועדה משותפת לבחון את מצב פליטי השואה ועתיד ארץ ישראל. הועדה המליצה על קבלה מיידית של 100,000 מעפילים לארץ, אך סירבה לתמוך במדינה יהודית מידית. ארה"ב ביקשה ליישם את ההמלצה; בריטניה תלתה אותה בתנאים פוליטיים, ונוצר פיצול שהחריף את הלחץ הבינלאומי.</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/המנדט_הבריטי</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A0%D7%93%D7%98_%D7%94%D7%91%D7%A8%D7%99%D7%98%D7%99</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>ועדת אנגלו-אמריקאית</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>כישלון הוועדה ומעבר לאו"ם</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>כישלון ועדת אנגלו-אמריקאית להוביל להסכמה בין-מעצמתית הוכיח שבריטניה לא יכולה עוד לנהל את הסכסוך לבדה. בשנת 1947 הפנתה בריטניה את השאלה לאו"ם. צעד זה פתח את הדרך להקמת אונסקו"פ ולתוכנית החלוקה שאושרה ב-29 בנובמבר 1947.</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/המנדט_הבריטי</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A0%D7%93%D7%98_%D7%94%D7%91%D7%A8%D7%99%D7%98%D7%99</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>ראשי ההנהגה</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>וייצמן כנשיא הראשון של ישראל</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>חיים וייצמן, שהוביל עשרות שנות דיפלומטיה ציונית ושיחק תפקיד מרכזי בהשגת הצהרת בלפור, נבחר לנשיא הראשון של מדינת ישראל (1948). תפקיד הנשיא מוגבל מוסדית, אך בחירתו מסמלת את הרציפות בין המאבק הציוני לבין ייסוד המדינה.</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/חיים_וייצמן</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%97%D7%99%D7%99%D7%9D_%D7%95%D7%99%D7%99%D7%A6%D7%9E%D7%9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>הכיבוש הסלאוקי</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>הכיבוש הסלאוקי וגזירות אנטיוכוס</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>אנטיוכוס הרביעי אפיפנס (מלך סוריה הסלאוקית, 175–164 לפנה"ס) כפה הלניזם על יהודה: אסר שמירת שבת, מילה ולימוד תורה, הקים מזבח זר בבית המקדש וחילל אותו. מדיניות זו, שבאה מתוך רצון לאחד את הממלכה תרבותית, נחשבת לניסיון ראשון בהיסטוריה לכפות זהות זרה על עם.</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/החשמונאים</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%97%D7%A9%D7%9E%D7%95%D7%A0%D7%90%D7%99%D7%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>מרד החשמונאים</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>מתתיהו ובניו – פרוץ המרד</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>מרד החשמונאים פרץ בידי מתתיהו הכהן ובניו בעיר מודיעין (167 לפנה"ס), שסירבו להקריב לאלילים. בנו יהודה המכבי הפך למנהיג המרד הצבאי, ניצל מאפיינים של לחימת גרילה בהרי יהודה, וניצח בסדרת קרבות צבאות סלאוקים גדולים ממנו.</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/החשמונאים</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%97%D7%A9%D7%9E%D7%95%D7%A0%D7%90%D7%99%D7%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>מרד החשמונאים</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>יהודה המכבי וחנוכת המקדש</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>ניצחונות יהודה המכבי אפשרו כיבוש ירושלים וטיהור בית המקדש מחרפת הפסל. ב-25 בכסלו 164 לפנה"ס חנך יהודה את המקדש מחדש – חנוכה. חגיגה זו הפכה לחג המבטא ניצחון הרוח היהודית והחירות הדתית, ואת הנס שנקשר בחזרת ה'חנוכייה'.</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/החשמונאים</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%97%D7%A9%D7%9E%D7%95%D7%A0%D7%90%D7%99%D7%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>מרד החשמונאים</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>ממרד לממלכה – יונתן ושמעון</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>לאחר מות יהודה המקביל השלימו אחיו יונתן ושמעון את הדרך לעצמאות. יונתן שילב דיפלומטיה ולחימה, ניצל את המחלוקות הסלאוקיות הפנימיות, ועלה לתפקיד הכהן הגדול. שמעון (הוכרז נשיא-כהן ב-141 לפנה"ס) קיבל הכרה בינלאומית מרומא ויוון, וביסס עצמאות מלאה.</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/החשמונאים</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%97%D7%A9%D7%9E%D7%95%D7%A0%D7%90%D7%99%D7%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>הכיבוש הרומי</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>גורמי המרד הגדול – פוליטיקה, כלכלה, דת</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>המרד הגדול (66–73) פרץ על רקע שילוב גורמים: שחיתות וגזל של הנציב הרומי פלורוס (שנטל כסף מאוצר המקדש), דיכוי ועינויים, מתחים חברתיים בין עניים לעשירים, וה'קנאים' שדחו שלטון זר על פי תפיסת 'מלכות האל'. כישלון הדיפלומטיה החמיר את המצב עד לפרוץ אש.</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/המרד_הגדול</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A8%D7%93_%D7%94%D7%92%D7%93%D7%95%D7%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>המרד הגדול</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>פלורוס הנציב וניצוץ המרד</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>הנציב הרומי גסיוס פלורוס (64–66) בלט בשחיתותו וחוסר רגישותו – לשיא, גזל 17 כיכר כסף מאוצר המקדש ב-66 לספירה. הפגנות עממיות ספגו תגובה אלימה. האווירה הצטברת של עלבון, דיכוי ואשמת עמלנות הנהיגה את ירושלים מהפגנה לפרוץ מרד גלוי.</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/המרד_הגדול</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A8%D7%93_%D7%94%D7%92%D7%93%D7%95%D7%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>תור הזהב</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>תור הזהב של יהדות ספרד – תנאים ורקע</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>בעשורים ה-10–11 לספירה, בעיקר בספרד המוסלמית (אנדלוסיה), חיו יהודים בתנאים של יחסית פתיחות ושגשוג – 'תור הזהב'. שיתוף פעולה תרבותי בין ערבים ויהודים, מעמד כלכלי ומינהלי גבוה, ופטרונות חכמים יצרו תנאים לפריחה מדעית, ספרותית ופילוסופית יהודית ייחודית.</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/יהדות_ספרד</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%99%D7%94%D7%93%D7%95%D7%AA_%D7%A1%D7%A4%D7%A8%D7%93</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>תור הזהב</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>גדולי יהדות ספרד המוסלמית</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>תור הזהב הוציא דמויות ענק: שמואל הנגיד (מדינאי, משורר, ראש ישיבה), ריה"ל (יהודה הלוי – משורר, פילוסוף, 'הכוזרי'), הרמב"ם (משה בן מיימון – פוסק, פילוסוף, 'מורה נבוכים') ועוד. חיבוריהם עיצבו את הפילוסופיה היהודית לדורות והמשיכו להשפיע על הגות יהודית ועולמית.</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/יהדות_ספרד</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%99%D7%94%D7%93%D7%95%D7%AA_%D7%A1%D7%A4%D7%A8%D7%93</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>תור הזהב</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>שקיעת תור הזהב ועלייתה של ספרד הנוצרית</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>תור הזהב שקע עם ירידת שלטון בני אומייה ועלייתה של ספרד הנוצרית (הרקונקיסטה). לחץ ההמרה והרדיפות בגרו להידרדרות, ועד שנת 1492 הפכה ספרד מרובדת שיא ליהדות למדינה שמגרשת אותה. 'אנוסים' המשיכו לשמור בסתר על יהדותם.</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/יהדות_ספרד</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%99%D7%94%D7%93%D7%95%D7%AA_%D7%A1%D7%A4%D7%A8%D7%93</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>גירוש ספרד</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>צו גירוש ספרד 1492</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>ב-31 במרץ 1492 חתמו הממלכים הקתוליים פרדיננד ואיזבלה על 'אדיקט האלהמברה' – הצו המגרש את כל יהודי ספרד. ליהודים ניתנו ארבעה חודשים להמיר דתם, למכור רכושם ולעזוב. כ-150,000–200,000 אנשים גורשו, לאחר מאות שנות ביסוס תרבותי ורוחני.</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/גירוש_ספרד</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%92%D7%99%D7%A8%D7%95%D7%A9_%D7%A1%D7%A4%D7%A8%D7%93</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>גירוש ספרד</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>גורמי הגירוש – דת, פוליטיקה, כלכלה</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>גירוש ספרד נבע משילוב: גורמים דתיים (חשש לנאמנות 'אנוסים', לחץ האינקוויזיציה, תפיסת אחידות דתית), פוליטיים (איחוד הממלכות תחת נצרות), וכלכליים (הכרת כספי היהודים לאוצר). הגירוש הביא לסיום 1,500 שנות נוכחות יהודית-רציפה בחצי האי האיברי.</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/גירוש_ספרד</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%92%D7%99%D7%A8%D7%95%D7%A9_%D7%A1%D7%A4%D7%A8%D7%93</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>גירוש ספרד</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>פיזור מגורשי ספרד ומרכזים חדשים</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>מגורשי ספרד נפוצו לכל עבר: האימפריה העות'מאנית קיבלה אותם בברכה (ב-1492 אמר הסולטאן 'כיצד אפשר לקרוא לפרדיננד חכם, הוא מעניי ממלכתי ומעשיר אוצרי?'). רבים התיישבו בסלוניקי, קושטא, ירושלים, צפת. 'לשון ספרדית' (לדינו) שמרה על הזכרון התרבותי עד המאה ה-20.</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/גירוש_ספרד</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%92%D7%99%D7%A8%D7%95%D7%A9_%D7%A1%D7%A4%D7%A8%D7%93</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>גירוש ספרד</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>השפעת הגירוש על היהדות הספרדית</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>גירוש ספרד הותיר רישום עמוק: צפת במאה ה-16 הפכה למרכז קבלה ומשפט (ר' יוסף קארו ו'השולחן ערוך', ר' יצחק לוריא). ה'ספרדים' שמרו על פי הלכה נפרד ועל תרבות ייחודית. הגירוש הפך לאחת מהזיכרונות הקולקטיביים המרכזיים של הזהות הספרדית.</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/גירוש_ספרד</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%92%D7%99%D7%A8%D7%95%D7%A9_%D7%A1%D7%A4%D7%A8%D7%93</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>שואה</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>מחנות</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>עבודת כפייה ומחנות ריכוז לפני מחנות ההשמדה</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>עוד לפני 'הפתרון הסופי' הפעיל המשטר הנאצי מחנות ריכוז (ראשון: דכאו, 1933) לכליאת מתנגדים פוליטיים, יהודים ו'אסוציאלים'. בתנאי קשיים, עינויים ועבודת כפייה שברו את הקורבנות. מחנות ריכוז אלה שימשו מודל ארגוני ועמדו בבסיס המערכת שהתפתחה לאחר מכן למחנות ההשמדה.</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/גרמניה_הנאצית</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%92%D7%A8%D7%9E%D7%A0%D7%99%D7%94_%D7%94%D7%A0%D7%90%D7%A6%D7%99%D7%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>שואה</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>ועידת אביאן</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>ועידת אביאן 1938 – כישלון ההצלה</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>ועידת אביאן (יולי 1938) כינסה 32 מדינות לדון בקבלת פליטים יהודים מגרמניה. למעט הרפובליקה הדומיניקנית, אף מדינה לא הציעה קבלה נרחבת. הכישלון חשף את אדישות העולם לגורל היהודים, חיזק את בידודם, ועודד את הנאצים להסיק שאין מי שיתנגד להחמרת הרדיפה.</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/השואה</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A9%D7%95%D7%90%D7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>שואה</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>אחרי השואה</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>משפטי נירנברג – שפיטת פושעים נאצים</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>משפטי נירנברג (1945–1946) היו משפטים שניהלו בעלות הברית נגד 24 מנהיגים נאצים בכירים. נקבעו אשמות חדשות: 'פשעים נגד השלום' (תכנון מלחמת תוקפנות), 'פשעי מלחמה' ו'פשעים נגד האנושות' – קטגוריה משפטית חדשה שכיסתה את השמדת היהודים. 12 נידונו למוות.</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/משפטי_נירנברג</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%A9%D7%A4%D7%98%D7%99_%D7%A0%D7%99%D7%A8%D7%A0%D7%91%D7%A8%D7%92</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>שואה</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>אחרי השואה</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>משפטי נירנברג ועיצוב המשפט הבינלאומי</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>משפטי נירנברג הניחו תשתית לאמנות בינלאומיות מרכזיות: האמנה למניעת רצח עם (1948), הצהרת זכויות האדם האוניברסלית (1948), ולימים חוקת בית הדין הפלילי הבינלאומי (רומא, 1998). הם קבעו עיקרון שמנהיגים אינם חסינים בפני שפיטה בינלאומית על פשעים נגד האנושות.</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/משפטי_נירנברג</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%A9%D7%A4%D7%98%D7%99_%D7%A0%D7%99%D7%A8%D7%A0%D7%91%D7%A8%D7%92</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>שואה</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>הצלה</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>מאפייני חסידי אומות העולם</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>חסידי אומות העולם הם לא-יהודים שסיכנו את חייהם להציל יהודים בשואה. מחקרים מראים שלא היה להם פרופיל דמוגרפי אחיד: גברים ונשים, כפריים ועירוניים, מכל שדרה חברתית. מניעיהם: אמונה דתית, ידידות אישית, עקרונות אנושיים. בולטים: אוסקר שינדלר, ראול ולנברג, יאנוש קורצ'אק.</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/חסידי_אומות_העולם</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%97%D7%A1%D7%99%D7%93%D7%99_%D7%90%D7%95%D7%9E%D7%95%D7%AA_%D7%94%D7%A2%D7%95%D7%9C%D7%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>שואה</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>הצלה</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>הנצחת חסידי אומות העולם ביד ושם</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>יד ושם בירושלים מוסמך מכוח חוק (1953) להכיר ב'חסידי אומות העולם' ולנציח אותם בגן הנצחה. עד היום הוכרו למעלה מ-28,000 חסידים. ייחוד ההנצחה: היא מדגישה שבתוך הרוע האנושי נשמרה אפשרות הבחירה המוסרית, ומנוגדת לנרטיב של 'כל העולם היה נגדנו'.</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/חסידי_אומות_העולם</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%97%D7%A1%D7%99%D7%93%D7%99_%D7%90%D7%95%D7%9E%D7%95%D7%AA_%D7%94%D7%A2%D7%95%D7%9C%D7%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>שואה</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>היקף</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>ממדי השואה – שישה מיליון</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>השואה הביאה לרצח כשישה מיליון יהודים – כשליש מיהדות העולם ב-1939. כ-3.3 מיליון מהם מפולין, שמקהלת יהדותה הגדולה נמחתה כמעט לחלוטין. קהילות שלמות שנבנו במשך מאות שנים – יהדות הולנד, יוון, הונגריה, ליטא – חוסלו. מדד זה הוא בסיס להבנת הייחודיות ההיסטורית של הטרגדיה.</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/השואה</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A9%D7%95%D7%90%D7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>שואה</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>ישוב ומדינה</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>השואה כגורם בהחלטת כ"ט בנובמבר</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>טבח היהודים ומצב שארית הפליטה לאחר 1945 הפכו לגורם בלתי-נפרד מהדיון הבינלאומי. הכרה מוסרית בכישלון העולם להציל את יהודי אירופה, לצד לחץ לפתרון מצב המחנות, הניעה חלק מהמדינות בהצבעת האו"ם לתמוך בחלוקה. לאחר השואה, הקמת מדינה יהודית נתפסה כתיקון מינימלי מוסרי.</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/השואה</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A9%D7%95%D7%90%D7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>מאורעות 1929</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>פרעות 1929 ומשמעותן הפוליטית</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>פרעות 1929 (בעיקר בחברון, ירושלים וצפת) פרצו על רקע מחלוקת על זכויות תפילה בכותל המערבי. הפרעות גרמו למאות הרוגים, חשפו את עומק העוינות הלאומית-הערבית, והניעו את בריטניה לעצב מדיניות מגבילה יותר (דוח הופ-סימפסון). ביישוב עוררו ויכוח על 'הבלגה' מול הגנה אקטיבית.</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/המנדט_הבריטי</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A0%D7%93%D7%98_%D7%94%D7%91%D7%A8%D7%99%D7%98%D7%99</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>מלחמת העצמאות</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>הסכמי שביתת הנשק 1949</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>עם סיום הלחימה נחתמו הסכמי שביתת נשק נפרדים עם מצרים, ירדן, לבנון וסוריה (1949). ההסכמים קבעו את 'הקו הירוק' – גבולות הפסקת האש – שנותרו גבול ישראל עד 1967. הם לא נחשבו להסדרי שלום (ממלכות ערב סירבו לשלום), אך עיגנו את קיומה של ישראל מבחינה מעשית.</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/מלחמת_העצמאות</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%9C%D7%97%D7%9E%D7%AA_%D7%94%D7%A2%D7%A6%D7%9E%D7%90%D7%95%D7%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>מלחמת העצמאות</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>הפליטים הפלסטינים – הנכבה</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>במהלך מלחמת העצמאות עזבו או גורשו כ-700,000 ערבים פלסטינים מבתיהם. הערבים מכנים את האירוע 'הנכבה' (האסון). גורמי הנדידה מורכבים: פחד, פקודות, לחץ צבאי. בעיית הפליטים הפלסטינים, שלא נפתרה, הפכה לאחת הסוגיות המרכזיות בסכסוך הישראלי-פלסטיני.</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/מלחמת_העצמאות</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%9C%D7%97%D7%9E%D7%AA_%D7%94%D7%A2%D7%A6%D7%9E%D7%90%D7%95%D7%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>ההכרעה הבינלאומית</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>הדיפלומטיה הציונית לקראת כ"ט בנובמבר</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>לפני ההצבעה ב-29 בנובמבר 1947 פעלה הסוכנות היהודית אינטנסיבית: שיכנוע משלחות קטנות, ניצול הרגישות שלאחר השואה, ולבסוף – תמיכת שני הגושים: ארה"ב ניצחה את קולות הדרום אמריקה, וברית המועצות ראתה בחלוקה צעד שיאיץ את הנסיגה הבריטית. ה-33 קולות בעד שינו היסטוריה.</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/תוכנית_החלוקה</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%AA%D7%95%D7%9B%D7%A0%D7%99%D7%AA_%D7%94%D7%97%D7%9C%D7%95%D7%A7%D7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>הקמת הצבא</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>הקמת צה"ל ופירוק המסגרות הנפרדות</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>עם הכרזת המדינה הוקם צבא הגנה לישראל (צה"ל) מ-26 במאי 1948 כצבא סדיר אחד. בן-גוריון פירק את הפלמ"ח כמסגרת עצמאית ואסר על פעולות חמושות מחוצה לו (פרשת אלטלנה). איחוד הכוחות חיוני היה לניהול מלחמה סדירה ולביסוס ריבונות המדינה.</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/דוד_בן-גוריון</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%93%D7%95%D7%93_%D7%91%D7%9F-%D7%92%D7%95%D7%A8%D7%99%D7%95%D7%9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>מבשרי הציונות</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>משה הס ולאומיות יהודית קדם-הרצלית</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>משה הס בספרו 'רומא וירושלים' (1862) היה מן הראשונים לנסח תפיסת לאומיות יהודית מודרנית: קרא להקמת קהילה יהודית עצמאית בארץ ישראל, משולבת עם תורת סוציאליזם. ספרו לא זכה להדים בזמנו, אך אחרי הרצל זוהה כמבשר, וגישתו השמאלנית-לאומנית שזרה ציונות ושאלה חברתית.</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/ציונות</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A6%D7%99%D7%95%D7%A0%D7%95%D7%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>מבשרי הציונות</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>לאון פינסקר ו'אוטואמנציפציה'</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>לאון פינסקר בחוברתו 'אוטואמנציפציה' (1882) ניתח את 'יהדופוביה' כמחלה חברתית מושרשת שאינה ניתנת לריפוי מבחוץ. הסיק שרק גאולה עצמית – ארגון לאומי ורכישת קרקע – תפתור את 'שאלת היהודים'. תפיסה זו קדמה לרצל ושימשה בסיס לתנועת חיבת ציון.</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/ציונות</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A6%D7%99%D7%95%D7%A0%D7%95%D7%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>ציונות</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>הציונות הסוציאליסטית</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>הציונות הסוציאליסטית שילבה מטרות לאומיות וחברתיות: להקים בארץ ישראל חברה יהודית מחדש, שוויונית ועובדת, המבוססת על 'כיבוש עבודה' ועבודת כפיים. גורדון הדגיש את 'דת העבודה' – טיהור הנפש דרך עבודת אדמה. ברנר וסירקין פיתחו את הזרם מתוך ביקורת הגלות. הציונות הסוציאליסטית הייתה הדומיננטית בתנועה העובדת.</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/ציונות</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A6%D7%99%D7%95%D7%A0%D7%95%D7%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>ציונות</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>הציונות הדתית</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>הציונות הדתית ('המזרחי', הרב קוק) ראתה בתחיית האומה 'ראשית צמיחת גאולתנו' – הכרזה שגאולת הגוף (המדינה) היא שלב בגאולה הדתית. בניגוד לחרדים שדחו את הציונות כמרידה, שיתפה פעולה עם ההנהגה הלאומית בבניין הארץ תוך שמירה על אופי דתי.</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/ציונות</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A6%D7%99%D7%95%D7%A0%D7%95%D7%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>הקונגרס הציוני</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>תוכנית באזל – תוכן ומשמעות</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>תוכנית באזל (1897) היא מצע יסוד הציונות: 'הציונות שואפת ליצור לעם היהודי בית לאומי בארץ ישראל, מובטח בחוק הציבורי'. בנוסף לנוסח, הקונגרס הקים מוסדות מתמשכים (ההסתדרות הציונית, קרן), גבה 'שקל' ומינה נהלי בחירות. הרצל רשם ביומנו שבבאזל ייסד מדינה יהודית.</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/הקונגרס_הציוני_העולמי_הראשון</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A7%D7%95%D7%A0%D7%92%D7%A8%D7%A1_%D7%94%D7%A6%D7%99%D7%95%D7%A0%D7%99_%D7%94%D7%A2%D7%95%D7%9C%D7%9E%D7%99_%D7%94%D7%A8%D7%90%D7%A9%D7%95%D7%9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>השכלה ואמנציפציה</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>כישלון האמנציפציה כזרז לציונות</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>בין 1860 ל-1880 נדמה היה שהאמנציפציה מצליחה: יהודים קיבלו שוויון זכויות רשמי בגרמניה, צרפת, אוסטריה. ואולם בשנות ה-80 התגבשה שוב האנטישמיות – פרעות ברוסיה (1881), מפלגות אנטישמיות, לאומנות גזעית. כישלון ההשתלבות שכנע חלק מהמשכילים כי הבעיה היא לאומית ולא תיפתר בהשכלה בלבד.</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/אנטישמיות</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%90%D7%A0%D7%98%D7%99%D7%A9%D7%9E%D7%99%D7%95%D7%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>בית המקדש</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>העלייה לרגל ומרכזיות ירושלים</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>בשלוש הרגלים (פסח, שבועות, סוכות) עלו יהודים מהארץ ומהתפוצות לירושלים, מה שהפך את בית המקדש למרכז לאומי-דתי מאחד. העלייה לרגל חיזקה קשרי זהות בין קהילות, תרמה לכלכלת ירושלים, ויצרה תחושת שייכות לאום. בחורבן המקדש אבדה עלייה זו ודרשה חלופות.</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/בית_המקדש_השני</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%91%D7%99%D7%AA_%D7%94%D7%9E%D7%A7%D7%93%D7%A9_%D7%94%D7%A9%D7%A0%D7%99</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>מרד בר כוכבא</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>מרד בר כוכבא – רקע ופרוץ</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>מרד בר כוכבא (132–135 לספירה) פרץ נגד הקיסר אדריאנוס, שאסר (כנראה) מילה ותכנן לבנות מושבה רומית על הריסות ירושלים. שמעון בר כוכבא הנהיג את המרד; ר' עקיבא קרא לו 'כוכבא' (מלך). המורדים הקימו שלטון-לאום עצמאי לשנה-שנתיים, אך הצבא הרומי בפיקוד יוליוס ספוורוס כרסם ודיכא את המרד.</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/מרד_בר_כוכבא</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%A8%D7%93_%D7%91%D7%A8_%D7%9B%D7%95%D7%9B%D7%91%D7%90</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>אחרי המרד</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>השלכות מרד בר כוכבא על יהדות</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>תבוסת מרד בר כוכבא (135) הביאה לחורבן יהודה: שם המחוז שונה ל'סוריה-פלשתינה', ירושלים הפכה ל'איליה קפיטולינה' ויהודים נאסרו מלגור בה, גזירות דת ('גזירות השמד') רדפו חכמים. עם זאת, מרכז הנהגה גלילי השתקם, ומה שנשמד הגדיר – רצף מנהיגות דתית עם מרכיב לאומי מחוק.</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/מרד_בר_כוכבא</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%A8%D7%93_%D7%91%D7%A8_%D7%9B%D7%95%D7%9B%D7%91%D7%90</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>כיתות מדבר יהודה</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>מגילות מדבר יהודה וחשיבותן</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>מגילות מדבר יהודה, שנתגלו מ-1947 באזור קומראן, הן הממצא הספרותי החשוב ביותר בעולם הקדום: כתבי יד עתיקים (החל מהמאה ה-3 לפנה"ס) של ספרי תנ"ך, יצירות כיתתיות ופרשנויות. הן מאפשרות הצצה ייחודית לגיוון הדתי-רעיוני של בית שני, ולהבנת עולמה של הכת (כנראה האיסיים).</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/האיסיים</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%90%D7%99%D7%A1%D7%99%D7%99%D7%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>יהדות אשכנז</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>מסעות הצלב ופרעות בקהילות אשכנז</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>מסעות הצלב (1096 ואילך) הביאו גל עוינות ליהודי אשכנז: קהילות שלמות (מיינץ, וורמס, שפיירא) נפרצו ויהודים נרצחו או בחרו בקידוש השם. אחרי גזירות תתנ"ו, גברה הפגיעות ונוצרו 'מחזורים' ו'קינות' שתיעדו את האסון. הפרעות עיצבו את הזיכרון הקולקטיבי ואת יחסי היהודים-נוצרים.</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/יהדות_אשכנז</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%99%D7%94%D7%93%D7%95%D7%AA_%D7%90%D7%A9%D7%9B%D7%A0%D7%96</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>מנהיגות רוחנית</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>רש"י ומרכזיות פירושו</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>רש"י (ר' שלמה יצחקי, צרפת, 1040–1105) כתב פירושים ממצים לתורה ולתלמוד שהפכו לכלי הלמדנות היסודי ביותר ביהדות אשכנז. פירושו ברור, תמציתי ומעשי. 'בעלי התוספות' שבאו אחריו פיתחו שיטת ויכוח ועיון בתלמוד ('תוספות'), ובצד רש"י יצרו את ציר הלמדנות האשכנזי.</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/יהדות_אשכנז</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%99%D7%94%D7%93%D7%95%D7%AA_%D7%90%D7%A9%D7%9B%D7%A0%D7%96</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>מרכזי יהדות</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>מרכז ספרד כחלופה לבבל</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>עם שקיעת מרכז בבל (המאה ה-11) עלה מרכז יהדות ספרד לבכורה. ספרד המוסלמית והנוצרית אכלסה קהילות יהודיות גדולות, שפיתחו הנהגה רוחנית עצמאית, ספרות, פילוסופיה ומשפט. מרכז ספרד קיים יותר מ-400 שנה, עד גירוש 1492 שפיזר חלק ממנה לאימפריה העות'מאנית ולצפון אפריקה.</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/גירוש_ספרד</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%92%D7%99%D7%A8%D7%95%D7%A9_%D7%A1%D7%A4%D7%A8%D7%93</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>סוגיות נבחרות</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>זיכרון השואה</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>יום הזיכרון לשואה ולגבורה</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>חוק 'יום הזיכרון לשואה ולגבורה – כ"ז בניסן' (1951, חוקק בכנסת 1959) קבע יום לאומי להנצחת ששת מיליון היהודים שנרצחו. הבחירה ב-27 בניסן – סמוך למרד גטו ורשה – מקשרת שואה להתנגדות ולגבורה. הזיכרון הלאומי לשואה הוא מרכיב מכונן בזהות הישראלית.</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/השואה</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A9%D7%95%D7%90%D7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>סוגיות נבחרות</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>חוקי יסוד</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>חוק יסוד: כבוד האדם וחירותו</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>חוק יסוד: כבוד האדם וחירותו (1992) מהווה אבן יסוד בהגנה על זכויות האדם בישראל: עיגן את ערך כבוד האדם, הזכות לחיים וחירות, פרטיות וקניין. הפסיקה שפיתחה בית המשפט העליון על בסיסו חיזקה את מעמד בית המשפט ואת בלימת חוקים פוגעניים. החוק הוא ציר ב'מהפכה החוקתית' הישראלית.</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/מדינת_ישראל</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%93%D7%99%D7%A0%D7%AA_%D7%99%D7%A9%D7%A8%D7%90%D7%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>סוגיות נבחרות</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>יחסי ישראל-תפוצות</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>הזיקה לתפוצות וחוק השבות</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>ישראל מגדירה עצמה כמדינת הלאום של כל היהודים: חוק השבות מאפשר לכל יהודי לעלות ולהתאזרח. הזיקה לתפוצות מבוטאת בתמיכה בקהילות, בחינוך ציוני, ובתיאום עם ארגונים כהסוכנות היהודית. מנגד, שאלות 'מיהו יהודי' ושאלות דת-ומדינה יוצרות מתחים עם חלק מהיהדות שבתפוצות.</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/חוק_השבות</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%97%D7%95%D7%A7_%D7%94%D7%A9%D7%91%D7%95%D7%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>העלייה השנייה</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>גורדון ו'דת העבודה'</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>אהרון דוד גורדון (עלייה שנייה) גיבש את 'דת העבודה': עבודת אדמה בידיים אינה רק אמצעי פרנסה אלא גאולה רוחנית-לאומית. יהודי הגלות ניתק מהטבע; החזרה לעבודת קרקע תחדש אותו. השקפתו השפיעה עמוקות על אידאולוגיית ההגשמה החלוצית ועל אתוס הקיבוץ.</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/העלייה_השנייה</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A2%D7%9C%D7%99%D7%99%D7%94_%D7%94%D7%A9%D7%A0%D7%99%D7%99%D7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>ניל"י</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>שרה אהרונסון ועקרון ה'קידוש השם' של ניל"י</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>שרה אהרונסון, פעילה מרכזית בניל"י, נתפסה ועונתה בידי הצאר לשמונה ימים, אך לא גילתה סודות הרשת. בסופו של דבר שמה קץ לחייה כדי לא לדבר. פועלה הפך לסמל מסירות ועמידה בפני עינויים. ניל"י נותר מוקד מחלוקת בציונות – בין הצלחה אינטלקטואלית לסיכון הביטחוני של ה'הגנה'.</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/ניל"י</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A0%D7%99%D7%9C%22%D7%99</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>הכיבוש הרומי</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>שיטת מסי הכיבוש הרומי</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>הכיבוש הרומי נשא עמו נטל מסים כבד: מס ראש (קפיטציה), מס קרקע (טריבוטום), ומסים מקומיים נוספים. גביית המסים הועברה לידי קבלנים (פובליקאנים) שגבו בשיטות קשות. העומס הכלכלי הפחית כלכלת קיום לרבים ביהודה, תרם לצמיחת שכבה מרוששת ולחלוקה חברתית שהזינה את המרד.</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/המרד_הגדול</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%9E%D7%A8%D7%93_%D7%94%D7%92%D7%93%D7%95%D7%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>אחרי החורבן</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>מרכזי יהדות אחרי 70 לספירה – גלות בבל, ספרד, רומא</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>לאחר חורבן בית שני התחזקו קהילות גולה קיימות וצמחו חדשות: בבל (שיפרחה לאחר מכן עם הגאונים), רומא, אלכסנדריה. כל קהילה פיתחה חיים יהודיים עצמאיים ואוטונומיים. 'הגלות' חייבה בניית מוסדות, סמכות ופסיקה שאינן תלויות בארץ ישראל – תהליך שהניח בסיס לקיום יהודי אורך-טווח.</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/רבן_יוחנן_בן_זכאי</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%A8%D7%91%D7%9F_%D7%99%D7%95%D7%97%D7%A0%D7%9F_%D7%91%D7%9F_%D7%96%D7%9B%D7%90%D7%99</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>יהדות אשכנז</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>הגירוש מאנגליה וצרפת וגלגולי הקהילות</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>יהודי אנגליה גורשו ב-1290, ויהודי צרפת גורשו בגלים ב-1306 ו-1394. גירושים אלה אילצו קהילות גדולות לנדוד מזרחה – לגרמניה ואחר כך לפולין ומזרח אירופה. הנדידה הזאת הניחה את הגרעין לקהילות ענק שצמחו שם, ועיצבה מחדש את מפת יהדות אירופה.</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/יהדות_אשכנז</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%99%D7%94%D7%93%D7%95%D7%AA_%D7%90%D7%A9%D7%9B%D7%A0%D7%96</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>שואה</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>שיטות ההשמדה</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>הגירוש מהונגריה – מהשמדה הגדולה ביותר</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>גירוש יהודי הונגריה (מאי–יולי 1944) היה השלב המהיר ביותר של ההשמדה: בתוך פחות מ-8 שבועות שולחו כ-440,000 יהודים לאושוויץ-בירקנאו, רובם הומתו עם הגעתם. שלב זה חל כש'הפתרון הסופי' כבר ידוע, ואנשים כוולנברג פעלו להצלה. זהו הסמל של 'שקיעת הרצח' עד הרגע האחרון.</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/הפתרון_הסופי</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%94%D7%A4%D7%AA%D7%A8%D7%95%D7%9F_%D7%94%D7%A1%D7%95%D7%A4%D7%99</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>שואה</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>הגטאות</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>אנמנואל רינגלבלום וארכיון 'עונג שבת'</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>ההיסטוריון עמנואל רינגלבלום ייסד בגטו ורשה את מחתרת התיעוד 'עונג שבת' (1940–1943). חוקרים, סופרים ואנשי ציבור אספו מסמכים, יומנים, ציורים ועדויות כדי לתעד את חיי הגטו. הארכיון נטמן בקופסאות חלב ונחשף אחרי המלחמה – עדות מרכזית לדרך ה'קידוש החיים' ולצורך לשמר את האמת.</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/גטו_ורשה</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%92%D7%98%D7%95_%D7%95%D7%A8%D7%A9%D7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>ביסוס המדינה</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>הכרת ארצות הברית ובריה"מ במדינת ישראל</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>שתי המעצמות הגדולות הכירו במדינת ישראל מהר: ארה"ב הכירה בה 11 דקות לאחר הכרזתה (טרומן, 14.5.1948); ברה"מ הכירה ימים ספורים לאחר מכן. הכרה זו העניקה לגיטימציה בינלאומית מיידית. שתי ההכרות נבעו ממניעים שונים: טרומן מרגש כלפי יהדות ועל רקע פנים-אמריקאי, ובריה"מ מאינטרס להרחיב השפעה על הבריטים.</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/מדינת_ישראל</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%93%D7%99%D7%A0%D7%AA_%D7%99%D7%A9%D7%A8%D7%90%D7%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>סוגיות נבחרות</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>עיצוב הכלכלה</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>כלכלת ישראל בשנותיה הראשונות – צנע ופיתוח</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>בשנים הראשונות התמודדה ישראל עם קשיים כלכליים: מלחמה, עלייה המונית, מחסור בסחורות ומט"ח. הונהגה שיטת 'הצנע' – קיצוב מזון ומוצרים. בו-זמנית הושקעו מאמצים בפיתוח תשתיות, חינוך ועיר. הסיוע האמריקאי (UJA) ורפרציות גרמניה (1952) שיחקו תפקיד מרכזי בהתאוששות.</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/מדינת_ישראל</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%9E%D7%93%D7%99%D7%A0%D7%AA_%D7%99%D7%A9%D7%A8%D7%90%D7%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>לאומיות</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>ארגוני השמירה</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>הקמת ה'הגנה' ומעמדה ביישוב</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>ה'הגנה' הוקמה ב-1920 כארגון צבאי-עממי הכפוף למוסדות הלאומיים (הסתדרות, ועד לאומי). שלא כ'השומר' הקטן והאליטיסטי, שאפה ה'הגנה' לחברות רחבה. עם הזמן פיתחה את 'הפלמ"ח' (פלוגות המחץ) ורכשה נשק. ה'הגנה' הייתה הגרעין שממנו צמח צה"ל ב-1948.</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/תנועת_המרי_העברי</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/%D7%AA%D7%A0%D7%95%D7%A2%D7%AA_%D7%94%D7%9E%D7%A8%D7%99_%D7%94%D7%A2%D7%91%D7%A8%D7%99</t>
         </is>
       </c>
     </row>

--- a/data/history_agent/source2_knowledge_base.xlsx
+++ b/data/history_agent/source2_knowledge_base.xlsx
@@ -1943,7 +1943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F169"/>
+  <dimension ref="A1:F213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7362,6 +7362,1414 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>הזרמים בחברה היהודית</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>הפרושים — תורה שבעל-פה וקרבה לעם</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>הפרושים היו הזרם הגדול והמשפיע ביותר בחברה היהודית בשלהי בית שני. עיקר ייחודם: אמונה בתורה שבעל-פה — מסורת פרשנית חיה שעוברת מדור לדור לצד התורה הכתובה — שאפשרה התאמת ההלכה לתנאים משתנים. הם האמינו בהישארות הנפש, בתחיית המתים, בשכר ועונש לאחר המוות ובשילוב של השגחה אלוהית עם בחירה חופשית. מבחינה חברתית ייצגו את מעמדות הביניים והעם הפשוט: מנהיגיהם — חכמים שמעמדם נקבע בלימוד ולא בייחוס — לימדו בבתי מדרש ובבתי כנסת. בימי שלומציון המלכה (76–67 לפנה״ס) שלטו בסנהדרין. מהפרושים צמחו הזוגות — ובהם הלל ושמאי — ולאחר החורבן הפכה תורתם ליהדות הרבנית: חכמי יבנה, התנאים והמשנה כולם המשך ישיר של המסורת הפרושית. הם היחידים מהזרמים ששרדו את החורבן.</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/המרד_הגדול</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>פרושים, צדוקים, איסיים וקנאים</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>הזרמים בחברה היהודית</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>הצדוקים — אצולת הכהונה והמקדש</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>הצדוקים — שנקראו כנראה על שם צדוק הכהן מימי דוד — היו זרם אצולת הכהונה והמשפחות העשירות בירושלים. עיקרי השקפתם: קבלת התורה הכתובה בלבד ודחיית התורה שבעל-פה של הפרושים; כפירה בהישארות הנפש, בתחיית המתים ובשכר ועונש לאחר המוות — 'אין לאדם אלא עולמו הזה'; והדגשת הבחירה החופשית המלאה של האדם. כוחם התרכז במקדש: הכהונה הגדולה הייתה ברובה צדוקית, והם שלטו בפולחן ובחצרות העשירים. מעמדם היה תלוי בקיום המקדש ובשיתוף פעולה עם השלטון — תחילה החשמונאי (ינאי תמך בהם) ואחר כך הרומי. ריחוקם מהעם הפשוט והישענותם על המקדש חרצו את גורלם: עם חורבן הבית בשנת 70 לספירה איבדו את בסיס קיומם ונעלמו מההיסטוריה — בעוד הפרושים, שמרכזם היה בית המדרש, שרדו.</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/המרד_הגדול</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>פרושים, צדוקים, איסיים וקנאים</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>הזרמים בחברה היהודית</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>האיסיים — קהילת הקודש במדבר</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>האיסיים היו זרם סגפני-פרישתי שמנה כמה אלפים. הם פרשו מירושלים ומחיי המקדש — שנחשבו בעיניהם מושחתים בידי כהונה פסולה — וחיו בקהילות שיתופיות, המוכרת שבהן בקומראן שעל חוף ים המלח. אורחות חייהם: שיתוף רכוש מלא — 'אין עשיר ואין עני', עבודה משותפת וסעודות טהרה; טבילות יומיות והקפדה קיצונית על טהרה; הימנעות רבים מהם מנישואין; וקבלה לקהילה רק לאחר שנות מבחן. בתאולוגיה האמינו בגזרה קדומה מוחלטת ובמלחמת קץ הימים בין 'בני האור' ל'בני החושך'. מרבית החוקרים מזהים את האיסיים עם כת קומראן שכתביה — מגילות ים המלח, שנתגלו ב-1947 — כוללים את 'סרך היחד', 'מגילת המלחמה' ועותקים עתיקים של ספרי המקרא. הקהילה חרבה בידי הרומאים במהלך המרד הגדול, כנראה בשנת 68 לספירה.</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/האיסיים</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>פרושים, צדוקים, איסיים וקנאים</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>הזרמים בחברה היהודית</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>הקנאים והסיקריים — האידאולוגיה של חירות בכל מחיר</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>הקנאים היו הזרם הלוחמני בחברה היהודית — 'הפילוסופיה הרביעית' בלשון יוסף בן מתתיהו. עיקרון יסוד: אין לקבל שלטון בשר ודם זר — 'אין אדון ליהודים אלא האל' — ולכן תשלום מס לרומא הוא בגידה דתית. ראשיתם במרד יהודה הגלילי נגד מפקד האוכלוסין של קויריניוס (6 לספירה). הסיקריים — פלג קיצוני שנקרא על שם הסיקה, פגיון קצר שהסתירו בבגדיהם — רצחו בירושלים משתפי פעולה יהודים עם רומא, ובהם הכהן הגדול יונתן. במרד הגדול היו הקנאים הכוח הדוחף: השתלטו על ירושלים, רצחו את מנהיגי המתונים ומנעו כל פשרה. הסיקריים בהנהגת אלעזר בן יאיר החזיקו במצדה עד שנת 73. ההיסטוריוגרפיה חלוקה ביחס אליהם: לוחמי חירות שהעדיפו מוות על שעבוד — או קיצונים שהאחריות לחורבן רובצת גם עליהם.</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/המרד_הגדול</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>פרושים, צדוקים, איסיים וקנאים</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>הסנהדרין</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>הסנהדרין — המוסד העליון של העם</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>הסנהדרין הייתה המוסד המשפטי-דתי העליון של העם היהודי בימי בית שני: 71 חכמים שישבו ב'לשכת הגזית' שבהר הבית. סמכויותיה: פרשנות התורה והכרעה במחלוקות הלכה; שיפוט בדיני נפשות ובמשפטי כוהן גדול, שבט ונביא שקר; עיבור השנה וקידוש החודש — שליטה בלוח השנה היהודי; ופיקוח על הכהונה והמקדש. בראשה עמדו הנשיא ואב בית הדין — בתקופת הזוגות הנהיגו אותה צמדים כהלל ושמאי. הרכבה שיקף את מאבק הזרמים: בתקופות שונות שלטו בה צדוקים או פרושים — בימי שלומציון הפכה פרושית. תחת השלטון הרומי צומצמו סמכויותיה — דיני נפשות ניטלו ממנה. לאחר החורבן התחדשה הסנהדרין ביבנה ואחר כך בגליל (אושא, ציפורי, טבריה) בראשות הנשיאים מבית הלל — והמשיכה לתפקד כהנהגת העם עד ביטולה במאה החמישית.</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/הסנהדרין</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>שיקום ההנהגה והדת לאחר החורבן</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>המרד הגדול</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>יוסף בן מתתיהו — מצביא, בוגד או היסטוריון</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>יוסף בן מתתיהו (37–100 לספירה לערך) — לימים יוספוס פלביוס — הוא המקור ההיסטורי המרכזי לתקופת בית שני ולמרד הגדול. כוהן ירושלמי משכיל, מונה בפרוץ המרד למפקד הגליל. לאחר נפילת יודפת (67) הסתתר במערה עם לוחמיו שנדרו למות; בהגרלת ההתאבדות נותר אחרון — ונכנע לרומאים. הוא ניבא לאספסיאנוס את הקיסרות, וכשהתגשמה הנבואה שוחרר, אימץ את שם משפחת הקיסר (פלביוס) וליווה את טיטוס במצור על ירושלים כמתורגמן ומשכנע-כניעה. בעם נחשב בוגד. ברומא כתב את ספריו: 'מלחמת היהודים' — תיאור המרד מעדות ראייה; 'קדמוניות היהודים' — תולדות העם; ו'נגד אפיון' — הגנה על היהדות. ההיסטוריונים נדרשים לזהירות: כתיבתו נועדה גם להצדיק את עצמו ולרצות את פטרוניו — אך בלעדיו ידיעתנו על התקופה הייתה דלה לאין ערוך.</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/המרד_הגדול</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>מהלך המרד, החורבן ומצדה</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>המרד הגדול</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>יודפת וקרבות הגליל 67 לספירה</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>הקרב על הגליל היה המערכה הראשונה בדיכוי המרד הגדול. אספסיאנוס ריכז בעכו צבא של כ-60,000 חיילים — שלושה לגיונות וכוחות עזר של מלכי החסות. יוסף בן מתתיהו, מפקד הגליל, ביצר ערים אך נמנע מקרב שדה מול הצבא הסדיר. העיר יודפת שבהרי הגליל התחתון עמדה במצור 47 ימים: המגינים הדפו מתקפות בקיר ובשמן רותח, אך הרומאים הבקיעו לבסוף בעזרת סוללת מצור. כ-40,000 נהרגו לפי יוסף; הוא עצמו נשבה. גמלא שברמת הגולן נפלה אחרי מצור קשה — אלפים מתושביה נהרגו או הוטלו מהמצוק. טבריה וציפורי נכנעו בלא קרב. בסוף 67 היה הגליל כולו בידי רומא. נפילת הגליל שלחה לירושלים זרם פליטים קנאים מרי נפש — שהציתו בעיר את מלחמת האחים שהחריבה אותה מבפנים עוד לפני בוא טיטוס.</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/המרד_הגדול</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>מהלך המרד, החורבן ומצדה</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>המרד הגדול</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>מצדה — המעוז האחרון 73 לספירה</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>מצדה — מבצר הורדוס על צוק מבודד במדבר יהודה — הייתה המעוז האחרון של המרד הגדול. בראשית המרד השתלטו עליה הסיקריים בהנהגת אלעזר בן יאיר, ואליהם הצטרפו פליטים מירושלים החרבה. בשנת 73 (או 74) צר עליה הנציב פלוויוס סילווה עם הלגיון העשירי: הרומאים הקיפו את ההר בחומת מצור ושמונה מחנות, ובנו סוללת עפר ענקית על המדרון המערבי. כשהובקעה החומה, נשא אלעזר בן יאיר — לפי יוסף בן מתתיהו — שני נאומים ששכנעו את 960 הנצורים למות בני חורין ולא ליפול לעבדות: הגברים המיתו את משפחותיהם, עשרה נבחרו בגורל להמית את השאר. שתי נשים וחמישה ילדים שהסתתרו נותרו לספר. חפירות יגאל ידין (1963–1965) חשפו את הארמונות, בית הכנסת והמקווה. מצדה הפכה בציונות לסמל: 'שנית מצדה לא תיפול'.</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/המרד_הגדול</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>מהלך המרד, החורבן ומצדה</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>הורדוס והנציבים</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>אגריפס הראשון ושלהי בית הורדוס</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>אגריפס הראשון, נכד הורדוס ומרים החשמונאית, היה המלך היהודי האחרון של יהודה (41–44 לספירה). את נעוריו בילה ברומא בחצר הקיסרים, וידידותו עם קליגולה וקלאודיוס הקנתה לו בהדרגה את כל ממלכת סבו. בניגוד להורדוס זכה לאהדת העם והפרושים: הקפיד על מצוות, הקריב במקדש, וחז״ל שימרו את זכרו לחיוב — 'אחינו אתה'. במשבר פסל קליגולה (40) פעל בחצר הקיסר לביטול הגזרה להציב פסל במקדש. הוא החל בבניית 'החומה השלישית' של ירושלים — שהרומאים עצרו מחשש למרד. מותו הפתאומי בקיסריה (44) סתם את הגולל על המלוכה: רומא החזירה את השלטון הישיר של הנציבים, הפעם על הארץ כולה. הנציבים האחרונים — פליקס, פסטוס, אלבינוס ופלורוס — היו מושחתים וכושלים, והידרדרות השלטון בשני העשורים שאחרי אגריפס הובילה ישירות למרד הגדול.</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/הורדוס</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>השלטון הישיר – תקופת הנציבים</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>מירושלים ליבנה</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>רבי עקיבא — מעם הארץ לגדול התנאים</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>רבי עקיבא בן יוסף (50–135 לספירה לערך) — גדול התנאים — החל ללמוד תורה רק בגיל 40, לפי המסורת בעידוד אשתו רחל, והפך לעמוד התווך של התורה שבעל-פה: שיטתו דרשה כל אות וכל תג בתורה, ותלמידיו ערכו את הגרסאות הראשונות של סדרי המשנה — 'סתם משנה כרבי עקיבא'. בזקנתו תמך במרד בר כוכבא: ראה בשמעון בר כוסבא את המלך המשיח — 'דרך כוכב מיעקב' — וקרא עליו 'זה הוא מלך המשיח', עמדה שחכמים אחרים דחו ('עקיבא, יעלו עשבים בלחייך ועדיין בן דוד לא יבוא'). לאחר כישלון המרד המשיך ללמד תורה בפומבי חרף גזרות אדריאנוס, נתפס והוצא להורג בעינויים בקיסריה — מת בקריאת שמע, 'בשעה שסרקו את בשרו במסרקות של ברזל'. הוא הראשון מ'עשרת הרוגי מלכות' וסמל מסירות הנפש על התורה.</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/מרד_בר_כוכבא</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>חכמי יבנה</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>בית שני</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>מירושלים ליבנה</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>רבי יהודה הנשיא וחתימת המשנה</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>רבי יהודה הנשיא (135–220 לספירה לערך) — 'רבי' או 'רבנו הקדוש' — חתם את המפעל שהחל ביבנה. כנשיא הסנהדרין בגליל (בית שערים וציפורי) ריכז בידיו עושר, סמכות תורנית וקשרים מצוינים עם השלטון הרומי — המסורת מספרת על ידידותו עם 'אנטונינוס' הקיסר. מפעל חייו: עריכת המשנה (כ-200 לספירה) — קיבוץ התורה שבעל-פה כולה, שנמסרה עד אז בעל-פה בנוסחים מתחרים, לחיבור אחד ערוך ומחולק לשישה סדרים: זרעים, מועד, נשים, נזיקין, קדשים, טהרות. העריכה מיינה הלכות לפי נושאים, הכריעה בין דעות ושימרה גם דעות מיעוט. חתימת המשנה הייתה מפנה היסטורי: התורה שבעל-פה קיבלה טקסט מוסמך שאפשר את לימודה בכל תפוצות ישראל — ועליו נבנו שני התלמודים, הבבלי והירושלמי. בכך הושלם המעבר מעם המקדש לעם הספר.</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/יהודה_הנשיא</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>שיקום ההנהגה והדת לאחר החורבן</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>בגדאד</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>הח'ליפות העבאסית — עלייתה ואופייה</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>השושלת העבאסית עלתה לשלטון בשנת 750 לאחר מרד שהפיל את בית אומיה. העבאסים — שייחסו עצמם לעבאס, דוד הנביא מוחמד — נשענו על תמיכת הפרסים ועל מורת הרוח מהאפליה שנהגו האומיים בלא-ערבים. השינוי שחוללו עמוק: מרכז הכובד עבר מדמשק מזרחה — אל עיראק, שם נוסדה בגדאד (762); האימפריה הפכה מ'ממלכה ערבית' לאימפריה אסלאמית רב-לאומית שבה פרסים, תורכים ואחרים שותפים בממשל; ופותח מנהל ריכוזי משוכלל בהנהגת הווזיר ובירוקרטיה של דיוואנים (משרדים). תור הזהב העבאסי — ימי הארון אל-רשיד (786–809) ובנו אל-מאמון — הצמיח כלכלה משגשגת, מדע ותרגום. מהמאה ה-10 נשחק כוחה: שושלות מקומיות התעצמו, והבויהים ואחריהם הסלג'וקים הפכו את הח'ליף לבובת חצר. הח'ליפות נפלה סופית בכיבוש המונגולי של בגדאד (1258).</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/הח'ליפות_העבאסית</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>בגדד כמרכז כלכלי ותרבותי</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>הקהילה היהודית בבגדאד</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>ישיבות סורא ופומבדיתא — מרכזי התורה של בבל</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>שתי הישיבות הגדולות של בבל — סורא, שייסד רב בשנת 219 לספירה, ופומבדיתא, שייסד רב יהודה בר יחזקאל — היו במשך כ-800 שנה מרכזי התורה של העולם היהודי. בהן נוצר ונערך התלמוד הבבלי (נחתם במאות 5–6), ובתקופת הגאונים (589–1038) עמדו בראשן הגאונים — הסמכות ההלכתית העליונה של כלל התפוצות. סדרי הלימוד היו ייחודיים: בחודשי הכלה — אדר ואלול, חודשי ההפוגה החקלאית — נהרו אלפי לומדים מרחבי בבל ומחוצה לה לישיבות, ונדונה מסכת שנקבעה מראש. הישיבות מומנו מתרומות התפוצות ומהכנסות אזורי שיפוט. במאות 9–10 עברו שתיהן לבגדאד הבירה — אך שמרו על שמותיהן. גדול גאוני סורא — רב סעדיה; גדולי פומבדיתא — רב שרירא ובנו רב האי, שעם מותו (1038) שקע מוסד הגאונות, וההגמוניה עברה למרכזים חדשים בספרד, צפון אפריקה ואשכנז.</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/הגאונים</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>ראש הגולה, הגאונים והישיבות</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>הקהילה היהודית בבגדאד</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>מחלוקת הלוח 922 — בבל מול ארץ ישראל</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>בשנת 921–922 פרצה המחלוקת החריפה ביותר בין מרכז בבל למרכז ארץ ישראל — על השליטה בלוח השנה. אהרן בן מאיר, ראש ישיבת ארץ ישראל, ביקש להשיב לארץ את הסמכות העתיקה לקביעת הלוח וקבע כללי עיבור שונים — שמשמעם הקדמת פסח וראש השנה בשני ימים. רב סעדיה — אז חכם צעיר בדרכו לבבל — יצא נגדו בחריפות לצד גאוני בבל וראש הגולה: שיגר איגרות לקהילות, חיבר את 'ספר המועדים' להפרכת שיטת בן מאיר, והזהיר מפני פילוג שבו יחוגו יהודים את החגים בתאריכים שונים. ואכן בשנת 922 חגגו חלק מהקהילות פסח בתאריך שונה. בתוך שנים הכריעה סמכותם של גאוני בבל: הלוח הבבלי-המחושב התקבל בכל התפוצות. המחלוקת סימנה את ניצחונה הסופי של בבל על ארץ ישראל כמרכז הסמכות של העם היהודי — ופרסמה את שמו של סעדיה, שמונה לגאון סורא שש שנים אחר כך.</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/סעדיה_גאון</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>ראש הגולה, הגאונים והישיבות</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>הקהילה היהודית בבגדאד</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>הקראים ומלחמת רס"ג בהם</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>התנועה הקראית — שראשיתה מיוחסת לענן בן דוד בבגדאד במאה ה-8 — דחתה את התורה שבעל-פה ואת סמכות התלמוד: 'חפשו בתורה היטב' — כל יהודי מפרש את המקרא בעצמו. הקראים דחו את ההלכה הרבנית בשבת (אסרו אש שהודלקה מערב שבת ואור בבית), במועדים (קידשו חודשים לפי ראיית ירח בפועל) ובדיני כשרות ועריות. התנועה התפשטה בבבל, בפרס, בארץ ישראל ובמצרים ואיימה על אחדות העם. רב סעדיה גאון הפך את המאבק בקראות למפעל חיים: עוד בצעירותו חיבר 'תשובות על ענן', ובהמשך פולמוסים שיטתיים שהוכיחו את נחיצות התורה שבעל-פה — שהרי המקרא עצמו אינו מפרש כיצד לקיים את מצוותיו. חיבוריו בלמו את התפשטות הקראות בקרב הרבניים והעמיקו את הקרע: הקראים נותרו כת נפרדת — ששרידיה קיימים עד ימינו — אך ההגמוניה הרבנית ניצלה.</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/סעדיה_גאון</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>ראש הגולה, הגאונים והישיבות</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>הקהילה היהודית בבגדאד</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>שקיעת מרכז בבל ונדידת ההגמוניה</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>מהמחצית השנייה של המאה ה-10 שקע מרכז בבל בהדרגה. הגורמים: היחלשות הח'ליפות העבאסית עצמה — הבויהים השתלטו על בגדאד (945) והמשק העיראקי הידרדר; ירידת התרומות מהתפוצות, שהעדיפו לטפח מרכזי תורה מקומיים; ועליית מרכזים חדשים ובהם קירואן שבצפון אפריקה, קורדובה שבספרד ומגנצא שבאשכנז. אגרת רב שרירא גאון (987) — תשובה לשאלת חכמי קירואן על השתלשלות המסורת — היא עצמה עדות לצורך להוכיח את סמכות בבל. סיפור 'ארבעת השבויים' שמביא אברהם אבן דאוד — ארבעה חכמים מבבל שנשבו ונפדו בקהילות שונות והקימו בהן ישיבות — משקף בדיעבד את תודעת המעבר. עם מות רב האי גאון (1038), אחרון גאוני פומבדיתא הגדולים, בטל מוסד הגאונות למעשה. הדגם הבבלי — תלמוד אחד מחייב וסמכות הלכתית מרכזית — המשיך לחיות בכל המרכזים שירשו אותה.</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/הגאונים</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>ראש הגולה, הגאונים והישיבות</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>יהדות ספרד</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>תור הזהב בספרד המוסלמית</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>בספרד המוסלמית (אל-אנדלוס) ידעה יהדות ספרד מהמאה ה-10 עד ה-12 פריחה חסרת תקדים — 'תור הזהב'. חסדאי אבן שפרוט, רופא ויועץ בחצר הח'ליף עבד א-רחמן השלישי בקורדובה, היה אב-הטיפוס של 'איש החצר' היהודי: דיפלומט, פטרון חכמים ומתכתב עם ממלכת הכוזרים. שמואל הנגיד הרחיק לכת ממנו: וזיר ממלכת גרנדה ומצביא צבאה — וגם משורר, פוסק הלכה ונשיא הקהילה. הסימביוזה עם תרבות ערב הולידה יצירה דו-לשונית: שירת חול וקודש בעברית במשקלים ערביים — שלמה אבן גבירול, משה אבן עזרא, ויהודה הלוי שחיבר את 'הכוזרי' ואת שירי ציון ('לבי במזרח ואנוכי בסוף מערב'); בלשנות עברית; פילוסופיה; והלכה — הרי״ף ותלמידיו. תור הזהב דעך עם פלישת המווחידון הקנאים (1148), שאילצו יהודים להתאסלם או לגלות — משפחת הרמב״ם נמלטה אז מקורדובה.</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/יהדות_ספרד</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>ייסוד ערים והיהודים</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>יהדות ספרד</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>גירוש ספרד 1492 — חורבן המרכז הגדול</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>ב-31 במרץ 1492 חתמו פרננדו ואיסבלה, 'המלכים הקתוליים', על צו אלהמברה: כל יהודי ספרד יתנצרו או יעזבו תוך ארבעה חודשים. הרקע: השלמת הרקונקיסטה בכיבוש גרנדה (ינואר 1492) שייתרה את ה'תועלת' היהודית; לחץ האינקוויזיציה שטענה כי היהודים מחזירים אנוסים ליהדותם; וקנאות דתית בהנהגת המלכה והנזיר טורקמדה. ניסיונות השתדלנות של דון יצחק אברבנאל, איש החצר וגדול הדור, נכשלו. בקיץ 1492 יצאו לגלות 100,000–200,000 יהודים — לפורטוגל (שם נכפתה עליהם המרה ב-1497), לצפון אפריקה, לאיטליה ולאימפריה העות'מאנית, שהסולטאן בייזיד השני קיבלם בברכה: 'מלך שמרושש את ארצו ומעשיר את ארצי'. הגירוש חתם אלף שנות יהדות ספרד והוליד את התפוצה הספרדית: שאלוניקי, איסטנבול, צפת — שם פרחו ההלכה (שולחן ערוך) והקבלה בידי המגורשים ובניהם.</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/גירוש_ספרד</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>ייסוד ערים והיהודים</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>אשכנז</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>גזירות תתנ"ו 1096 — מסע הצלב הראשון והקהילות</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>במסע הצלב הראשון, באביב-קיץ 1096 (שנת תתנ"ו), השמידו המוני צלבנים את קהילות הריינוס בדרכם לארץ הקודש. ההיגיון הרצחני: 'מדוע נלך להילחם בכופרים בירושלים כשרוצחי ישו יושבים בינינו?'. בשפיירא הציל ההגמון את רוב הקהילה; בוורמייזא נרצחו כ-800 יהודים בשני גלים; במגנצא — הקהילה הגדולה והמפוארת — נרצחו יותר מאלף, לאחר שההגמון שהבטיח הגנה נמלט. רבים בחרו במוות על קידוש השם: המיתו את ילדיהם ואת עצמם ובלבד שלא יוטבלו — מעשה שתועד בפיוטי הקינה ובכרוניקות העבריות ('ויעקדו בנים ובנות'). הקיסר היינריך הרביעי התיר לאנוסים לשוב ליהדותם. הגזירות לא חיסלו את יהדות אשכנז — הקהילות שוקמו תוך דור — אך טבעו בה תודעת קידוש השם ועיצבו את זיכרון השואה הקהילתי בתפילות 'אב הרחמים' ו'יזכור'.</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/גזירות_תתנ"ו</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>אשכנז, תקנות הקהילה וגזירות תתנ"ו</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>אשכנז</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>רבנו גרשום מאור הגולה ותקנותיו</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>רבנו גרשום בן יהודה (960–1028 לערך), ראש ישיבת מגנצא, כונה 'מאור הגולה' — אבי יהדות אשכנז הלמדנית. ישיבתו משכה תלמידים מכל אירופה — בהם רבותיו של רש״י — והערותיו ביססו את נוסח התלמוד באשכנז. עיקר השפעתו: התקנות המיוחסות לו ('חרם דרבנו גרשום') שעיצבו את חיי הקהילה האשכנזית: איסור נשיאת שתי נשים — ביגמיה, שהייתה מותרת מן התורה ונהוגה בארצות האסלאם; איסור גירוש אישה בעל כורחה; איסור קריאת מכתבי הזולת; ואיסור הזכרת חטאם של אנוסים ששבו ליהדות — תקנה שנגעה לבנו שלו, שהומר בכפייה. התקנות התקבלו בכל קהילות אשכנז וצרפת בתוקף חרם — נידוי חברתי מוחלט על העובר עליהן — והפכו לעמוד התווך של המשפחה האשכנזית. הן מדגימות את כוחה של ההנהגה הרבנית ליצור חקיקה מחייבת בלא מדינה, בכוח הסמכות התורנית והקהילתית בלבד.</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/רבנו_גרשום</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>אשכנז, תקנות הקהילה וגזירות תתנ"ו</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>אשכנז</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>הקהל — מוסדות האוטונומיה באשכנז</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>הקהילה האשכנזית — 'הקהל' — הייתה תאגיד אוטונומי שניהל את כל תחומי החיים היהודיים. מוסדותיה: פרנסים וטובי העיר — הנהגה נבחרת מבעלי הבתים משלמי המס, שניהלה את ענייני הציבור; בית הדין — שפט לפי ההלכה בכל ענייני הפנים, ופנייה לערכאות גויים נחשבה עבירה חמורה; ומערכת שירותים מסועפת: בית כנסת, מקווה, חברה קדישא, הכנסת כלה, ביקור חולים, תלמוד תורה וקופת צדקה. כלי האכיפה המרכזי — החרם: נידוי שמשמעו מוות חברתי, שכן היהודי לא יכול היה להתקיים מחוץ לקהילה. 'תקנות הקהל' הסדירו מסים, מסחר ואף הגבלות על מותרות. 'חזקת היישוב' אפשרה לקהילה למנוע התיישבות יהודים חדשים — הגנה על מטה לחמם של הקיימים. הדגם הקהילתי האשכנזי — שלטון עצמי מלא בלא טריטוריה — היה מהמפותחים שידעה ההיסטוריה היהודית.</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/יהדות_אשכנז</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>אשכנז, תקנות הקהילה וגזירות תתנ"ו</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>ערים וקהילות</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>אשכנז</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>עלילות הדם ומעמד 'עבדי האוצר'</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>מהמאה ה-12 הידרדר מעמד יהודי אשכנז. עלילת הדם הראשונה — נוריץ' שבאנגליה, 1144: היהודים הואשמו ברצח ילד נוצרי לשימוש פולחני בדמו. העלילה — שהכנסייה הרשמית דחתה לא פעם אך המון העם אימץ — נדדה ברחבי אירופה (בלואה 1171, פולדא 1235, לינקולן 1255) וגבתה מאות קורבנות; אליה נוספו עלילת חילול לחם הקודש והאשמת היהודים בהרעלת בארות בימי המגפה השחורה (1348–1350), שבעקבותיה הושמדו מאות קהילות. במקביל עוגן מעמד 'עבדי האוצר' (servi camerae regis): היהודים הוגדרו רכוש הקיסר — הוא חב בהגנתם והם חבים לו מסים כרצונו. המעמד סיפק הגנה בימי שגרה אך הפך את היהודים לנכס סחיר: קיסרים משכנו 'את יהודיהם' לנסיכים ולערים, וכשפחת ערכם הכלכלי — גורשו: אנגליה 1290, צרפת 1306 ו-1394, וערי גרמניה בזו אחר זו במאה ה-15.</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/יהדות_אשכנז</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>אשכנז, תקנות הקהילה וגזירות תתנ"ו</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>הספר הלבן</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>הספר הלבן 1939 — סגירת שערי הארץ</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>בעקבות המרד הערבי הגדול (1936–1939) ומסקנות ועדת פיל פרסמה ממשלת בריטניה במאי 1939 'ספר לבן' שסימן מפנה אנטי-ציוני חד. עיקריו: הגבלת העלייה היהודית ל-75,000 בלבד בחמש שנים — ולאחריהן עלייה רק בהסכמה ערבית; הגבלות חמורות על רכישת קרקעות בידי יהודים ברוב שטחי הארץ; והבטחה להקים תוך עשר שנים מדינה ארץ-ישראלית אחת עם רוב ערבי. תזמונו היה הרה אסון: ערב מלחמת העולם השנייה, כשיהודי אירופה חיפשו נואשות מפלט. בן-גוריון ניסח את המדיניות הציונית: 'נילחם בהיטלר כאילו אין ספר לבן, ונילחם בספר הלבן כאילו אין היטלר'. במהלך המלחמה התגייסו כ-30,000 מבני היישוב לצבא הבריטי — ובמקביל אורגנה עלייה בלתי-חוקית. אחרי המלחמה, כשממשלת הלייבור המשיכה לאכוף את הספר הלבן על ניצולי השואה, הפך המסמך למוקד המאבק בבריטים.</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/הספר_הלבן_(1939)</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>הספר הלבן, ההעפלה ותנועת המרי</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>תנועת המרי העברי</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>תנועת המרי העברי 1945–1946 — המאבק המאוחד</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>באוקטובר 1945, לאחר שהתברר כי ממשלת הלייבור ממשיכה במדיניות הספר הלבן, הוקמה 'תנועת המרי העברי' — מסגרת מאוחדת של שלושת הארגונים: ההגנה (עם הפלמ״ח), האצ״ל והלח״י, בתיאום הנהגת היישוב. פעולותיה: 'ליל הרכבות' (נובמבר 1945) — חבלה במסילות בכל רחבי הארץ; שחרור 208 מעפילים ממחנה המעצר בעתלית בידי הפלמ״ח; 'ליל הגשרים' (יוני 1946) — פיצוץ אחד-עשר גשרים שחיברו את הארץ לשכנותיה. הבריטים הגיבו ב'שבת השחורה' (29 ביוני 1946): כ-17,000 חיילים עצרו אלפים מההנהגה ומהפלמ״ח וערכו חיפושי נשק נרחבים. בעקבות פיצוץ מלון המלך דוד בידי האצ״ל (יולי 1946, 91 הרוגים) — פעולה שחרגה מהמתואם — פירקה ההנהגה את תנועת המרי. המאבק נמשך בנתיב ההעפלה וההתיישבות, שהפגין את צדקת הדרישה הציונית בלא לאבד את אהדת העולם.</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/תנועת_המרי_העברי</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>הספר הלבן, ההעפלה ותנועת המרי</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>ההעפלה</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>ההעפלה 1945–1948 — היקף, שיטה ומשמעות</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>ההעפלה — העלייה הבלתי-חוקית בניגוד לחוקי הספר הלבן — הפכה אחרי המלחמה לזרוע המרכזית של המאבק הציוני. המוסד לעלייה ב' של ההגנה ארגן בשנים 1945–1948 כ-65 הפלגות ובהן כ-70,000 מעפילים, רובם ניצולי שואה ממחנות העקורים. השיטה: רכישת אוניות רעועות, איסוף מעפילים בנמלי איטליה, צרפת ויוון, והפלגה לעבר חופי הארץ — מול מצור הצי הבריטי. רוב האוניות נתפסו; מאוגוסט 1946 גירשו הבריטים את המעפילים למחנות מעצר בקפריסין, שם הוחזקו כ-52,000 יהודים מאחורי גדרות תיל עד קום המדינה. דווקא הכישלון ה'מבצעי' היה הצלחה מדינית: תמונות ניצולי השואה הנאבקים בחיילים בריטים ומגורשים למחנות הסעירו את דעת הקהל העולמית, הביכו את בריטניה והוכיחו לוועדות הבינלאומיות כי אין פתרון לשאלת העקורים בלא מדינה יהודית.</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8245&amp;chapterid=803</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>הספר הלבן, ההעפלה ותנועת המרי</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>ההעפלה</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>פרשת אקסודוס יולי 1947 — הסמל שהכריע</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>האונייה 'אקסודוס מאירופה 1947' ('יציאת אירופה') הפליגה מצרפת ביולי 1947 ועל סיפונה 4,515 מעפילים — ניצולי שואה. מול חופי הארץ השתלטו עליה משחתות בריטיות בקרב שבו נהרגו שלושה מעפילים. בניגוד לנוהג הגירוש לקפריסין, החליט שר החוץ בווין 'ללמד לקח' ולהחזיר את המעפילים לנמל המוצא: הם הועברו לשלוש אוניות גירוש שהפליגו לצרפת — שם סירבו המעפילים לרדת, והצרפתים סירבו להורידם בכוח. אחרי שלושה שבועות של מצור ימי עגנו האוניות בהמבורג שבגרמניה — והמעפילים הורדו בכוח על אדמת גרמניה, מראה שזעזע את העולם: ניצולי שואה מוחזרים בכוח בריטי לארץ הרוצחים. הפרשה התרחשה בדיוק בימי ביקור ועדת אונסקו״פ בארץ — חבריה צפו במחזות דומים בנמל חיפה — והשפיעה ישירות על המלצתם לסיים את המנדט ולהקים מדינה יהודית.</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8245&amp;chapterid=803</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>ועדת אונסקו"פ והחלטת החלוקה</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>הוועדה האנגלו-אמריקאית</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>ועדת החקירה האנגלו-אמריקאית 1946</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>בנובמבר 1945, תחת לחץ הנשיא טרומן שדרש לאפשר כניסת 100,000 עקורים לארץ, הסכימה בריטניה להקים ועדת חקירה משותפת — שישה בריטים ושישה אמריקאים — לבחינת שאלת ארץ ישראל ומצב העקורים. הוועדה ביקרה במחנות העקורים בגרמניה — שם התרשמה כי כמעט כולם רוצים רק בארץ ישראל — וגבתה עדויות בארץ, ובהן עדויות בן-גוריון וויצמן. בדו״ח (מאי 1946) המליצה: כניסה מיידית של 100,000 עקורים; ביטול הגבלות הקרקע של הספר הלבן; והמשך משטר נאמנות — בלא מדינה יהודית ולא ערבית. טרומן אימץ פומבית את סעיף ה-100,000; ראש ממשלת בריטניה אטלי התנה את הביצוע בפירוק המחתרות מנשקן — ובפועל קבר את הדו״ח. כישלון הוועדה שכנע את ההנהגה הציונית שאין להיתלות בבריטניה, והאיץ את ההסלמה: ליל הגשרים, השבת השחורה — והדרך לאו״ם.</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/ועדת_אנגלו-אמריקאית</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>הספר הלבן, ההעפלה ותנועת המרי</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>החלטת כ"ט בנובמבר</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>תגובות היישוב, הפלסטינים ומדינות ערב להחלטת החלוקה</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>החלטת כ״ט בנובמבר התקבלה ביישוב בשמחה עצומה — המונים רקדו ברחובות כל הלילה. אך ההנהגה פיכחה: בן-גוריון, שלא יצא לחגוג, ידע שהערבים יפתחו במלחמה. בעיות התוכנית מבחינת היישוב: כ-30 יישובים יהודיים — וירושלים עצמה — מחוץ לתחומי המדינה היהודית; גבולות ארוכים ומפותלים בשלושה גושים עם מעברים צרים; מיעוט ערבי גדול בתוך המדינה היהודית; ואובדן נכסים אסטרטגיים כתחנת הכוח בנהריים ומפעל האשלג הצפוני. התגובה הערבית הייתה דחייה מוחלטת: הוועד הערבי העליון הכריז שביתה כללית בת שלושה ימים, והליגה הערבית — שהחליטה עוד לפני ההצבעה — החלה לרכז צבא מתנדבים בגבולות. למחרת ההצבעה, 30 בנובמבר 1947, נורה אוטובוס יהודי ליד שדה התעופה לוד ושישה נוסעים נרצחו — הירייה הפותחת של מלחמת העצמאות.</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8245&amp;chapterid=809</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>ועדת אונסקו"פ והחלטת החלוקה</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>מלחמת העצמאות</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>השלב הראשון — מלחמת השיירות וגוש עציון</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>בשלב הראשון של מלחמת העצמאות (דצמבר 1947 – מרץ 1948) הייתה היוזמה בידי הערבים, והמערכה התרכזה בדרכים. כוחות ערביי הארץ, ולצדם 'צבא ההצלה' של קאוקג'י שחדר מהמדינות השכנות, תקפו את התחבורה היהודית: הדרכים לירושלים, לנגב ולגליל המערבי הפכו למלכודות מוות. ההגנה, שדבקה בעיקרון שאין נוטשים יישוב, נאלצה ללוות כל נסיעה בשיירות מאובטחות — והמלווים שילמו ביוקר: שיירת הל״ה (ינואר 1948) — 35 לוחמי פלמ״ח וחי״ש שיצאו רגלית לתגבר את גוש עציון הנצור — נתגלתה, כותרה ולחמה עד הסוף; כל לוחמיה נפלו. שיירת יחיעם בגליל ושיירת חולדה נפגעו קשות; בסוף מרץ נחסמה הדרך לירושלים כליל ושיירת נבי דניאל איבדה את רוב משורייניה. גוש עציון עצמו נפל בי״ד באייר — יום לפני הכרזת המדינה: 127 ממגיניו נהרגו, רובם בטבח לאחר הכניעה, והשאר נפלו בשבי הירדני.</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8245&amp;chapterid=3692</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>שלבי המלחמה והכרזת העצמאות</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>מלחמת העצמאות</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>מבצע יואב אוקטובר 1948 — פריצת הדרך לנגב</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>מבצע יואב (15–22 באוקטובר 1948) נועד לפרוץ את הדרך לנגב הנצור ולהכריע את הצבא המצרי שחצץ בין מרכז הארץ ליישובי הדרום. הרקע: בהפוגה השנייה ניתק הצבא המצרי את הנגב, וישראל חששה שהסדר מדיני יקבע את קווי החזית כגבולות קבע. בפיקוד יגאל אלון, מפקד חזית הדרום, תקפו שלוש חטיבות — גבעתי, הנגב ויפתח — ולראשונה הופעל חיל האוויר בהיקף נרחב נגד שדות התעופה המצריים. ההכרעה: כיבוש משלטי חוליקאת פתח את 'ציר הרוחב' אל הנגב; ב-21 באוקטובר נכבשה באר שבע — בירת הנגב — והכוח המצרי נחתך לשניים. חטיבה מצרית שלמה כותרה ב'כיס פלוג'ה' (בה שירת הקצין גמאל עבד אל-נאצר, לימים נשיא מצרים). המבצע קבע את אחיזת ישראל בנגב — ובהמשכו, במבצעי חורב (דצמבר 1948) ועובדה (מרץ 1949), הושלמה ההשתלטות עד אילת.</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/מבצע_יואב</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>שלבי המלחמה והכרזת העצמאות</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>מגילת העצמאות</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>מגילת העצמאות — מבנה, תוכן ומשמעות</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>מגילת העצמאות, שהוקראה בידי בן-גוריון ב-14 במאי 1948 במוזיאון תל אביב, בנויה משלושה חלקים. החלק ההיסטורי מנמק את זכות העם היהודי למדינה: הקשר ההיסטורי לארץ — 'בארץ ישראל קם העם היהודי'; העליות וההתיישבות; הצהרת בלפור והמנדט; השואה; מאבק המעפילים; והחלטת האו״ם מכ״ט בנובמבר. החלק האופרטיבי מכריז: 'אנו מכריזים בזאת על הקמת מדינה יהודית בארץ ישראל, היא מדינת ישראל'. החלק ההצהרתי מתווה את דמות המדינה: פתוחה לעלייה יהודית ולקיבוץ גלויות; שקודה על פיתוח הארץ לטובת כל תושביה; מושתתת על חירות, צדק ושלום לאור חזונם של נביאי ישראל; מקיימת שוויון זכויות חברתי ומדיני גמור לכל אזרחיה בלי הבדל דת, גזע ומין; ומבטיחה חופש דת, מצפון, לשון, חינוך ותרבות. המגילה איננה חוקה, אך בית המשפט העליון העניק לעקרונותיה מעמד פרשני מחייב — ומ-1994 הן מעוגנות בחוקי היסוד.</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/מגילת_העצמאות</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>שלבי המלחמה והכרזת העצמאות</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>מלחמת העצמאות</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>הקרב על ירושלים — מצור, לטרון ודרך בורמה</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>ירושלים הייתה זירת ההכרעה הקשה של מלחמת העצמאות. 100,000 יהודי העיר היו תלויים בשיירות מהשפלה — ומדצמבר 1947 הלך המצור והתהדק: מים בקיצוב, לחם במנות, והפגזות בלתי פוסקות של הלגיון הירדני. מבצע נחשון (אפריל 1948) פרץ את הדרך זמנית, אך משטרת לטרון — ששלטה על הכביש — נותרה בידי הלגיון חרף התקפות ישראליות חוזרות שגבו מאות נפגעים. הפתרון: 'דרך בורמה' — דרך עפר חלופית שנפרצה בהרים דרומית ללטרון ביוני 1948, ימים לפני ההפוגה הראשונה — ודרכה זרמו מזון, תחמושת ותגבורות שהצילו את העיר המערבית. הרובע היהודי בעיר העתיקה לא ניצל: לאחר קרבות בתים מרים נכנע ב-28 במאי 1948 — תושביו פונו, מגיניו נשבו ובתי הכנסת חרבו. בסיום המלחמה נחצתה ירושלים: המערבית ישראלית; המזרחית — והכותל המערבי — בידי ירדן, עד 1967.</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8245&amp;chapterid=3692</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>שלבי המלחמה והכרזת העצמאות</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>הקמת המדינה</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>הסכמי שביתת הנשק</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>הסכמי רודוס 1949 — סיום המלחמה והקו הירוק</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>מלחמת העצמאות הסתיימה לא בהסכמי שלום אלא בארבעה הסכמי שביתת נשק שנחתמו ב-1949 בתיווך האו״ם — רובם באי רודוס, בהובלת המתווך ראלף באנץ' (שזכה על כך בפרס נובל לשלום). מצרים חתמה ראשונה (24 בפברואר): רצועת עזה נותרה בידיה וכוחותיה המכותרים בפלוג'ה שוחררו. לבנון (23 במרץ): הגבול הבינלאומי הוחזר. ירדן (3 באפריל): הגדה המערבית וירושלים המזרחית נותרו בידי הלגיון — וסופחו לירדן ב-1950; ישראל קיבלה את ואדי ערה ואת 'המשולש'. סוריה חתמה אחרונה (20 ביולי): נסוגה משטחים שכבשה תמורת פירוזם. קווי שביתת הנשק — 'הקו הירוק' — הקיפו כ-78% מהארץ המנדטורית והפכו לגבולותיה המוכרים של ישראל עד 1967. ההסכמים הוגדרו צבאיים-זמניים 'עד להסדר של שלום' — שלא בא: מדינות ערב התמידו בסירובן להכיר בישראל, והסכסוך נמשך.</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8245&amp;chapterid=804</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>שלבי המלחמה והכרזת העצמאות</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>סוגיות נבחרות</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>מלחמת ששת הימים</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>ההסלמה של מאי 1967 — צעדי נאצר</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>בחודשיים שלפני מלחמת ששת הימים הסלים המשבר בארבעה צעדים מצריים. הרקע: באפריל 1967 הפיל חיל האוויר הישראלי שישה מטוסים סוריים בקרב אווירי, וברית המועצות העבירה למצרים מידע כוזב שישראל מרכזת כוחות לתקיפת סוריה. בתגובה: (א) ב-14 במאי הזרים נאצר כוחות גדולים לסיני — בעיצומו של מצעד יום העצמאות בירושלים; (ב) ב-19 במאי דרש ופינה את כוח החירום של האו״ם שישב בסיני מאז 1957 לשמירת הפירוז — והאו״ם נענה מיד, מה שהקפיץ את יוקרת נאצר בעולם הערבי; (ג) ב-23 במאי סגר את מצרי טיראן לשיט ישראלי — ניתוק נמל אילת, שישראל הגדירה מראש עילת מלחמה (casus belli); (ד) ב-30 במאי חתם מלך ירדן חוסיין על ברית הגנה שהעמידה את צבאו תחת פיקוד מצרי, ואליה הצטרפה עיראק. כך נסגרה סביב ישראל חזית ערבית משולשת — והמלחמה הפכה לשאלה של זמן.</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8270&amp;chapterid=2159</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>חברה, ממשל וביטחון</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>סוגיות נבחרות</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>מלחמת ששת הימים</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>תקופת ההמתנה וממשלת הליכוד הלאומי</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>שלושת השבועות שבין סגירת מצרי טיראן לפרוץ המלחמה — 'תקופת ההמתנה' — היו מהקשים בתולדות ישראל. צה״ל גייס את מערך המילואים והמשק קפא; בעורף נחפרו שוחות ובתי קברות הוכשרו לקליטת אלפי חללים אפשריים; נאומו המהוסס של ראש הממשלה לוי אשכול ברדיו ('הנאום המגומגם') העמיק את החרדה הציבורית. ישראל פנתה לארצות הברית ולמעצמות המערב בבקשה לפתוח את המצרים בכוח בינלאומי — כפי שהובטח ב-1957 — אך נענתה בבקשות איפוק. בלחץ הציבור והמערכת הפוליטית הוקמה ב-1 ביוני ממשלת ליכוד לאומי: מפלגות האופוזיציה — גח״ל בראשות בגין ורפ״י — צורפו לממשלה, ומשה דיין מונה לשר הביטחון, מינוי שהשיב את ביטחון הציבור. ב-4 ביוני החליטה הממשלה על מתקפת מנע, ולמחרת בבוקר יצא חיל האוויר למבצע 'מוקד'.</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8270&amp;chapterid=2159</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>חברה, ממשל וביטחון</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>סוגיות נבחרות</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>מלחמת ששת הימים</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>מבצע מוקד ושישה ימי לחימה</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>ב-5 ביוני 1967 בשעה 07:45 יצא חיל האוויר הישראלי למבצע 'מוקד': מתקפת פתע על שדות התעופה של מצרים — בשעה שבה הטייסים המצרים בארוחת הבוקר ומסכי המכ״ם מנמיכים כוננות. תוך שלוש שעות הושמד עיקר חיל האוויר המצרי על הקרקע — כ-300 מטוסים; בהמשך היום הושמדו גם חילות האוויר של סוריה וירדן שנכנסו ללחימה. העליונות האווירית המוחלטת אפשרה הכרעה מהירה בשלוש חזיתות: בדרום כבש צה״ל בארבעה ימים את כל חצי האי סיני והגיע לתעלת סואץ; במרכז — לאחר שירדן פתחה באש על ירושלים חרף אזהרת ישראל — נכבשו ירושלים המזרחית (כולל הר הבית והכותל, 7 ביוני) וכל הגדה המערבית; בצפון נכבשה רמת הגולן בקרב קשה (9–10 ביוני). בשישה ימים שילשה ישראל את שטחה — מהניצחונות הצבאיים המהירים והמוחצים בהיסטוריה המודרנית.</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8270&amp;chapterid=2159</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>חברה, ממשל וביטחון</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>סוגיות נבחרות</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>מלחמת ששת הימים</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>תוצאות ששת הימים — אופוריה, שטחים ומחלוקת</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>תוצאות מלחמת ששת הימים עיצבו את ישראל לדורות. במישור הביטחוני: עומק אסטרטגי חדש — הגבול הורחק ממרכזי האוכלוסייה לתעלת סואץ, לירדן ולרמה; ובחברה השתררה אופוריה ותחושת אל-מעצור — שאננות שתתנקם בישראל ב-1973. במישור הלאומי-דתי: איחוד ירושלים והשיבה לכותל המערבי ולמקומות הקדושים עוררו התרוממות רוח משיחית — וצמיחת תנועת ההתנחלות בשטחים. במישור המדיני: תחת שליטת ישראל נמצאו כמיליון פלסטינים, ונפתח הוויכוח האידאולוגי המכונן — 'שטחים תמורת שלום' או 'ארץ ישראל השלמה' — שמפלג את הפוליטיקה הישראלית עד היום. ועידת חרטום הערבית (ספטמבר 1967) השיבה ב'שלושת הלאווים': לא שלום, לא הכרה, לא משא ומתן עם ישראל. החלטת מועצת הביטחון 242 (נובמבר 1967) קבעה את נוסחת 'שטחים תמורת שלום' כבסיס לכל הסדר עתידי.</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8270&amp;chapterid=2159</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>חברה, ממשל וביטחון</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>סוגיות נבחרות</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>המלחמה הקרה במזרח התיכון</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>המעצמות, מירוץ החימוש והדרך למלחמות</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>המלחמה הקרה עיצבה את הסכסוך הערבי-ישראלי משנות ה-50. ברית המועצות, שתמכה בהקמת ישראל ב-1947, עברה לצד הערבי: 'עסקת הנשק הצ'כית' עם מצרים (1955) פתחה מירוץ חימוש שהציף את האזור בנשק סובייטי מתקדם — מטוסי מיג, טנקים וטילים — לצבאות מצרים וסוריה, ולווה ביועצים סובייטיים. ארצות הברית ומדינות המערב חיזקו בהדרגה את ישראל — תחילה צרפת (שסיפקה את מטוסי המיראז' ואת הכור בדימונה) ומ-1967 ואילך ארצות הברית. המעורבות הסובייטית הציתה גם את משבר 1967: המידע הכוזב שמסרה מוסקבה לקהיר על ריכוזי צבא ישראליים מול סוריה הניע את שרשרת ההסלמה. הדפוס חזר ב-1973: הנשק הסובייטי איפשר למצרים וסוריה לתקוף, והרכבת האווירית האמריקאית חימשה את ישראל במהלך המלחמה — והאזור הפך לזירת העימות החמה של המלחמה הקרה.</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8270&amp;chapterid=2159</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>חברה, ממשל וביטחון</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>סוגיות נבחרות</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>מלחמת יום הכיפורים</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>ועדת אגרנט — חקר המחדל</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>ב-21 בנובמבר 1973, בלחץ זעם ציבורי גואה, הוקמה ועדת חקירה ממלכתית לבדיקת מחדלי המלחמה בראשות נשיא בית המשפט העליון שמעון אגרנט. הוועדה התמקדה בכשל המודיעיני: אמ״ן החזיק ב'קונספציה' — ההנחה שמצרים לא תתקוף לפני שתשיג יכולת אווירית (לא לפני 1975) — ולכן פירש את ריכוזי הצבא המצרי כתרגיל, וקבע עד בוקר המלחמה 'סבירות נמוכה למלחמה'. דו״ח הביניים (אפריל 1974) הטיל אחריות אישית על ראש אמ״ן אלי זעירא וסגנו, על הרמטכ״ל דוד אלעזר ועל מפקד פיקוד הדרום — והמליץ על הדחתם. את הדרג המדיני — גולדה מאיר ושר הביטחון דיין — פטרה הוועדה מאחריות ישירה, קביעה שעוררה סערה ציבורית: תנועות מחאה של חיילים משוחררים (מוטי אשכנזי) דרשו את התפטרות הממשלה. ב-11 באפריל 1974 התפטרה גולדה מאיר, וממשלתה נפלה עמה — והדרך נסללה לרבין ובהמשך למהפך 1977.</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8270&amp;chapterid=827</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>חברה, ממשל וביטחון</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>סוגיות נבחרות</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>עלייה לישראל</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>הגורמים לעלייה ההמונית בשנות ה-50 וה-60</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>מיליון עולים הגיעו לישראל עד 1960 — והגורמים נבדלו בין התפוצות. מאירופה: ניצולי השואה ממחנות העקורים, שאירופה הפכה בעבורם לבית קברות משפחתי ולא ראו בה עוד בית; והשתלטות ברית המועצות על מזרח אירופה, שעוררה גלי יציאה — בפולין אף אפשר השלטון הקומוניסטי (גומולקה) את יציאת היהודים. מארצות האסלאם: ההתלהבות הדתית-משיחית מהקמת המדינה — רבים ראו בה ובניצחון במלחמה אתחלתא דגאולה; פרעות והתפרצויות אלימות שערערו את ביטחון הקהילות; והדה-קולוניזציה — היציאה מהחסות האירופית הפכה את היהודים לחשודים בעיני התנועות הלאומיות הערביות. בשנות ה-60 נוספו גלים בעקבות ניצחון ששת הימים שמיצב את ישראל כמקום בטוח: עלייה ממרוקו (בהגמשת מדיניות המלך חסן השני) ומארגנטינה (על רקע אנטישמיות). העלייה הכפילה את האוכלוסייה — והעמידה את המדינה הצעירה במבחן קליטה אדיר.</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8270&amp;chapterid=828</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>העלייה ההמונית, המעברות וכור ההיתוך</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>סוגיות נבחרות</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>עלייה לישראל</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>שלושה דפוסי ארגון העלייה מארצות האסלאם</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>העלייה מארצות האסלאם — כ-70% מיהודי ארצות אלו עלו לישראל — אורגנה בשלושה דפוסים לפי מצב הקהילה. עליית הצלה ('חיסול גלויות'): בלוב, תימן ועיראק, שבהן נשקפה סכנה ממשית ליהודים, הועלו קהילות שלמות במהירות ובתיאום עם השלטון המקומי — 'מרבד הקסמים' הטיס כ-49,000 מיהודי תימן (1949–1950), ו'עזרא ונחמיה' העלה כ-120,000 מיהודי עיראק (1950–1951) שנדרשו לוותר על אזרחותם ורכושם. עלייה מבוקרת: ממרוקו, תוניסיה, טורקיה ואיראן — שבהן לא נשקפה סכנה מיידית — הונהגה מ-1952 סלקציה: קדימות לצעירים, בריאים ובעלי כושר עבודה, מחשש לקריסת מערכות הקליטה. המדיניות פיצלה משפחות — זקנים ונכים הושארו מאחור — ונותרה פצע בזיכרון העדתי. עלייה חשאית: מסוריה, לבנון ומצרים, שאסרו יציאת יהודים, הוברחו יהודים בסתר — בים, ביבשה ובאוויר.</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8270&amp;chapterid=829</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>העלייה ההמונית, המעברות וכור ההיתוך</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>סוגיות נבחרות</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>עלייה לישראל</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>חוק השבות 1950 — זכות העלייה כיסוד המדינה</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>חוק השבות, שהתקבל בכנסת פה אחד ב-5 ביולי 1950 — יום פטירת הרצל — הוא מאבני היסוד של ישראל כמדינה יהודית: 'כל יהודי זכאי לעלות ארצה'. החוק הפך את עקרון קיבוץ הגלויות ממשאלה הצהרתית במגילת העצמאות לזכות משפטית מוקנית: יהודי אינו 'מהגר' אלא שב למולדתו, ואשרת עולה נשללת רק ממי שפועל נגד העם היהודי או מסכן את הציבור. חוק האזרחות (1952) השלים: עולה מקבל אזרחות מיד עם עלייתו. תיקון מס' 2 (1970) — בעקבות פרשת האח דניאל והלכת שליט — הגדיר 'יהודי' לעניין החוק: מי שנולד לאם יהודייה או התגייר ואינו בן דת אחרת, והרחיב את הזכות לבן/בת זוג, לילדים ולנכדים של יהודי ולבני זוגם — הרחבה שאפשרה את העלייה הגדולה מברית המועצות לשעבר. החוק מגלם את ייעוד המדינה כבית לאומי — ומעורר עד היום ויכוחים על 'מיהו יהודי'.</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>https://he.wikipedia.org/wiki/חוק_השבות</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>ממלכתיות, דת ומדינה ומעמד המיעוטים</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>סוגיות נבחרות</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>קליטת העלייה</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>הצנע והקיצוב 1949–1959 — כלכלת קליטה במחסור</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>מדיניות הצנע הונהגה באפריל 1949 כדי לאפשר למדינה בת השנה לקלוט עלייה המונית בלא קריסה כלכלית. הרקע: קופה ריקה אחרי מלחמת העצמאות, יתרות מטבע חוץ אפסיות — והכפלת האוכלוסייה תוך שלוש שנים. השיטה: קיצוב (רציונינג) של מזון ומוצרי יסוד בנקודות — כל תושב קיבל תלושים לכמות שווה של לחם, סוכר, שמן, ביצים ובשר (מנה שתוכננה על 2,600 קלוריות ליום); פיקוח על מחירים; והקצאת מטבע חוץ ריכוזית. משרד הקיצוב והאספקה בראשות דב יוסף הפך למוסד הנודע — והשנוא — במדינה. תופעות הלוואי: 'שוק שחור' משגשג שהמדינה נלחמה בו במשפטים ובמודיעים; תורים, תחליפים ('ביצת אבקה') ומרירות ציבורית שתרמה לתבוסת מפא״י בבחירות העירוניות (1950). מ-1953, עם ייצוב המשק וכספי השילומים מגרמניה, הוקל הקיצוב בהדרגה — ובוטל סופית ב-1959. הצנע נחרת כסמל תקופת החלוציות הכפויה של שנות המדינה הראשונות.</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8270&amp;chapterid=830</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>העלייה ההמונית, המעברות וכור ההיתוך</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>סוגיות נבחרות</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>קליטת העלייה</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>פתרונות הדיור — ממחנות העולים לעיירות הפיתוח</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>בעיית הדיור הייתה האתגר המיידי של קליטת 700,000 העולים: למדינה לא היו דירות למאות אלפים, ובמקביל נדרש פיזור אוכלוסין לאזורי ספר בעלי חשיבות ביטחונית. הפתרונות התפתחו בשלבים: תחילה שוכנו עולים במחנות צבא בריטיים נטושים ובמחנות עולים (1948–1950) — אולמות צפופים ואוהלים בתנאי תברואה ירודים, שבהם הייתה התלות בסוכנות מלאה; אחרים נקלטו בבתים ערביים נטושים ביפו, חיפה, רמלה ולוד. ב-1950, ביוזמת לוי אשכול, הוקמו המעברות — 62 ברחבי הארץ — שיכוני ביניים של אוהלים, פחונים ובהמשך צריפים ליד יישובים ותיקים, שבהם נדרשה כל משפחה לפרנס את עצמה. השלב הקבוע: כ-30 עיירות פיתוח שהוקמו בפריפריה — קריית שמונה, בית שאן, דימונה, אופקים — ויישובי 'שרשרת ביטחון' לאורך הגבולות. הפיזור פתר את מצוקת הדיור אך קיבע ריבוד גאוגרפי-עדתי שמלווה את ישראל עד היום.</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>https://campus.ort.org.il/mod/book/view.php?id=8270&amp;chapterid=830</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>העלייה ההמונית, המעברות וכור ההיתוך</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
